--- a/output/version3/test/25-15/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1120</v>
+        <v>1145</v>
       </c>
       <c r="C2" t="n">
-        <v>1027</v>
+        <v>1111</v>
       </c>
       <c r="D2" t="n">
-        <v>1034</v>
+        <v>1172</v>
       </c>
       <c r="E2" t="n">
-        <v>1073</v>
+        <v>1159</v>
       </c>
       <c r="F2" t="n">
-        <v>1295</v>
+        <v>1095</v>
       </c>
       <c r="G2" t="n">
-        <v>1105</v>
+        <v>1150</v>
       </c>
       <c r="H2" t="n">
-        <v>1110</v>
+        <v>1083</v>
       </c>
       <c r="I2" t="n">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="J2" t="n">
-        <v>1110</v>
+        <v>1139</v>
       </c>
       <c r="K2" t="n">
-        <v>1076</v>
+        <v>1112</v>
       </c>
       <c r="L2" t="n">
-        <v>1111.2</v>
+        <v>1133.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1047</v>
+        <v>1059</v>
       </c>
       <c r="C3" t="n">
-        <v>1054</v>
+        <v>1162</v>
       </c>
       <c r="D3" t="n">
-        <v>1119</v>
+        <v>1231</v>
       </c>
       <c r="E3" t="n">
-        <v>1111</v>
+        <v>1078</v>
       </c>
       <c r="F3" t="n">
-        <v>1135</v>
+        <v>1110</v>
       </c>
       <c r="G3" t="n">
-        <v>1220</v>
+        <v>1099</v>
       </c>
       <c r="H3" t="n">
-        <v>1056</v>
+        <v>1030</v>
       </c>
       <c r="I3" t="n">
-        <v>1109</v>
+        <v>1145</v>
       </c>
       <c r="J3" t="n">
-        <v>1100</v>
+        <v>1079</v>
       </c>
       <c r="K3" t="n">
-        <v>1134</v>
+        <v>1069</v>
       </c>
       <c r="L3" t="n">
-        <v>1108.5</v>
+        <v>1106.2</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1157</v>
+        <v>1255</v>
       </c>
       <c r="C4" t="n">
-        <v>1114</v>
+        <v>1086</v>
       </c>
       <c r="D4" t="n">
-        <v>1058</v>
+        <v>1184</v>
       </c>
       <c r="E4" t="n">
-        <v>1104</v>
+        <v>1194</v>
       </c>
       <c r="F4" t="n">
-        <v>1062</v>
+        <v>971</v>
       </c>
       <c r="G4" t="n">
-        <v>1194</v>
+        <v>1158</v>
       </c>
       <c r="H4" t="n">
         <v>1130</v>
       </c>
       <c r="I4" t="n">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="J4" t="n">
-        <v>1137</v>
+        <v>1029</v>
       </c>
       <c r="K4" t="n">
-        <v>938</v>
+        <v>1284</v>
       </c>
       <c r="L4" t="n">
-        <v>1103.7</v>
+        <v>1144.7</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>865</v>
+        <v>915</v>
       </c>
       <c r="C5" t="n">
-        <v>913</v>
+        <v>1049</v>
       </c>
       <c r="D5" t="n">
-        <v>962</v>
+        <v>937</v>
       </c>
       <c r="E5" t="n">
-        <v>934</v>
+        <v>976</v>
       </c>
       <c r="F5" t="n">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="G5" t="n">
-        <v>998</v>
+        <v>959</v>
       </c>
       <c r="H5" t="n">
-        <v>990</v>
+        <v>903</v>
       </c>
       <c r="I5" t="n">
-        <v>978</v>
+        <v>949</v>
       </c>
       <c r="J5" t="n">
-        <v>909</v>
+        <v>873</v>
       </c>
       <c r="K5" t="n">
-        <v>1175</v>
+        <v>959</v>
       </c>
       <c r="L5" t="n">
-        <v>964.9</v>
+        <v>945.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>1077</v>
       </c>
       <c r="C6" t="n">
-        <v>1077</v>
+        <v>1220</v>
       </c>
       <c r="D6" t="n">
-        <v>1155</v>
+        <v>1229</v>
       </c>
       <c r="E6" t="n">
+        <v>1086</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1170</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1193</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="J6" t="n">
         <v>1145</v>
       </c>
-      <c r="F6" t="n">
-        <v>1075</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1346</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1096</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1025</v>
-      </c>
-      <c r="J6" t="n">
-        <v>913</v>
-      </c>
       <c r="K6" t="n">
-        <v>1209</v>
+        <v>1150</v>
       </c>
       <c r="L6" t="n">
-        <v>1107.8</v>
+        <v>1149.5</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="C7" t="n">
+        <v>965</v>
+      </c>
+      <c r="D7" t="n">
         <v>987</v>
       </c>
-      <c r="C7" t="n">
-        <v>948</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1043</v>
-      </c>
       <c r="E7" t="n">
-        <v>1104</v>
+        <v>977</v>
       </c>
       <c r="F7" t="n">
-        <v>999</v>
+        <v>869</v>
       </c>
       <c r="G7" t="n">
-        <v>983</v>
+        <v>1057</v>
       </c>
       <c r="H7" t="n">
-        <v>1055</v>
+        <v>1195</v>
       </c>
       <c r="I7" t="n">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="J7" t="n">
-        <v>1089</v>
+        <v>986</v>
       </c>
       <c r="K7" t="n">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="L7" t="n">
-        <v>1025.8</v>
+        <v>1020.9</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1143</v>
+        <v>1081</v>
       </c>
       <c r="C8" t="n">
-        <v>972</v>
+        <v>1181</v>
       </c>
       <c r="D8" t="n">
-        <v>1137</v>
+        <v>1028</v>
       </c>
       <c r="E8" t="n">
-        <v>1046</v>
+        <v>1077</v>
       </c>
       <c r="F8" t="n">
-        <v>1061</v>
+        <v>1139</v>
       </c>
       <c r="G8" t="n">
-        <v>1030</v>
+        <v>1096</v>
       </c>
       <c r="H8" t="n">
-        <v>1036</v>
+        <v>1097</v>
       </c>
       <c r="I8" t="n">
-        <v>1157</v>
+        <v>984</v>
       </c>
       <c r="J8" t="n">
-        <v>1086</v>
+        <v>1041</v>
       </c>
       <c r="K8" t="n">
-        <v>952</v>
+        <v>1139</v>
       </c>
       <c r="L8" t="n">
-        <v>1062</v>
+        <v>1086.3</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>969</v>
+        <v>947</v>
       </c>
       <c r="C9" t="n">
-        <v>1067</v>
+        <v>1049</v>
       </c>
       <c r="D9" t="n">
-        <v>971</v>
+        <v>874</v>
       </c>
       <c r="E9" t="n">
-        <v>985</v>
+        <v>1046</v>
       </c>
       <c r="F9" t="n">
-        <v>901</v>
+        <v>960</v>
       </c>
       <c r="G9" t="n">
-        <v>1030</v>
+        <v>999</v>
       </c>
       <c r="H9" t="n">
-        <v>1003</v>
+        <v>911</v>
       </c>
       <c r="I9" t="n">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="J9" t="n">
-        <v>1166</v>
+        <v>939</v>
       </c>
       <c r="K9" t="n">
-        <v>897</v>
+        <v>1011</v>
       </c>
       <c r="L9" t="n">
-        <v>995.5</v>
+        <v>971.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1028</v>
+        <v>973</v>
       </c>
       <c r="C10" t="n">
-        <v>1018</v>
+        <v>1041</v>
       </c>
       <c r="D10" t="n">
-        <v>962</v>
+        <v>1079</v>
       </c>
       <c r="E10" t="n">
-        <v>1083</v>
+        <v>1125</v>
       </c>
       <c r="F10" t="n">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="G10" t="n">
-        <v>1053</v>
+        <v>1068</v>
       </c>
       <c r="H10" t="n">
-        <v>1057</v>
+        <v>1011</v>
       </c>
       <c r="I10" t="n">
-        <v>1056</v>
+        <v>1173</v>
       </c>
       <c r="J10" t="n">
-        <v>1020</v>
+        <v>1061</v>
       </c>
       <c r="K10" t="n">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="L10" t="n">
-        <v>1042.2</v>
+        <v>1068.1</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1206</v>
+        <v>1166</v>
       </c>
       <c r="C11" t="n">
-        <v>1137</v>
+        <v>988</v>
       </c>
       <c r="D11" t="n">
-        <v>1113</v>
+        <v>1186</v>
       </c>
       <c r="E11" t="n">
-        <v>1026</v>
+        <v>1129</v>
       </c>
       <c r="F11" t="n">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="G11" t="n">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="H11" t="n">
-        <v>1155</v>
+        <v>1146</v>
       </c>
       <c r="I11" t="n">
-        <v>1118</v>
+        <v>1079</v>
       </c>
       <c r="J11" t="n">
-        <v>1159</v>
+        <v>1036</v>
       </c>
       <c r="K11" t="n">
-        <v>1104</v>
+        <v>1179</v>
       </c>
       <c r="L11" t="n">
-        <v>1134.9</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="C12" t="n">
-        <v>1031</v>
+        <v>1128</v>
       </c>
       <c r="D12" t="n">
-        <v>1022</v>
+        <v>1114</v>
       </c>
       <c r="E12" t="n">
-        <v>1372</v>
+        <v>1115</v>
       </c>
       <c r="F12" t="n">
-        <v>1129</v>
+        <v>1055</v>
       </c>
       <c r="G12" t="n">
-        <v>1103</v>
+        <v>1237</v>
       </c>
       <c r="H12" t="n">
-        <v>1038</v>
+        <v>1066</v>
       </c>
       <c r="I12" t="n">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="J12" t="n">
-        <v>1169</v>
+        <v>1204</v>
       </c>
       <c r="K12" t="n">
-        <v>1422</v>
+        <v>1122</v>
       </c>
       <c r="L12" t="n">
-        <v>1143.9</v>
+        <v>1117.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1180</v>
+        <v>1073</v>
       </c>
       <c r="C13" t="n">
-        <v>1124</v>
+        <v>978</v>
       </c>
       <c r="D13" t="n">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>1111</v>
       </c>
       <c r="F13" t="n">
-        <v>1135</v>
+        <v>1214</v>
       </c>
       <c r="G13" t="n">
-        <v>1263</v>
+        <v>1185</v>
       </c>
       <c r="H13" t="n">
-        <v>1265</v>
+        <v>1022</v>
       </c>
       <c r="I13" t="n">
-        <v>1139</v>
+        <v>1202</v>
       </c>
       <c r="J13" t="n">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="K13" t="n">
-        <v>1260</v>
+        <v>1183</v>
       </c>
       <c r="L13" t="n">
-        <v>1203.9</v>
+        <v>1131.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>935</v>
+        <v>876</v>
       </c>
       <c r="C14" t="n">
-        <v>988</v>
+        <v>952</v>
       </c>
       <c r="D14" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E14" t="n">
-        <v>1138</v>
+        <v>1185</v>
       </c>
       <c r="F14" t="n">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="G14" t="n">
-        <v>815</v>
+        <v>1091</v>
       </c>
       <c r="H14" t="n">
-        <v>1024</v>
+        <v>979</v>
       </c>
       <c r="I14" t="n">
-        <v>1112</v>
+        <v>1039</v>
       </c>
       <c r="J14" t="n">
-        <v>1078</v>
+        <v>1030</v>
       </c>
       <c r="K14" t="n">
-        <v>1076</v>
+        <v>1276</v>
       </c>
       <c r="L14" t="n">
-        <v>1025.5</v>
+        <v>1054.9</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1122</v>
+        <v>1062</v>
       </c>
       <c r="C15" t="n">
-        <v>1160</v>
+        <v>1417</v>
       </c>
       <c r="D15" t="n">
-        <v>1035</v>
+        <v>1022</v>
       </c>
       <c r="E15" t="n">
-        <v>1085</v>
+        <v>1162</v>
       </c>
       <c r="F15" t="n">
-        <v>1042</v>
+        <v>928</v>
       </c>
       <c r="G15" t="n">
-        <v>1037</v>
+        <v>1091</v>
       </c>
       <c r="H15" t="n">
-        <v>1197</v>
+        <v>1218</v>
       </c>
       <c r="I15" t="n">
-        <v>1008</v>
+        <v>1082</v>
       </c>
       <c r="J15" t="n">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="K15" t="n">
-        <v>999</v>
+        <v>1043</v>
       </c>
       <c r="L15" t="n">
-        <v>1068.7</v>
+        <v>1103.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="C16" t="n">
-        <v>976</v>
+        <v>1020</v>
       </c>
       <c r="D16" t="n">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="E16" t="n">
-        <v>1267</v>
+        <v>1026</v>
       </c>
       <c r="F16" t="n">
-        <v>1090</v>
+        <v>1162</v>
       </c>
       <c r="G16" t="n">
-        <v>1086</v>
+        <v>1044</v>
       </c>
       <c r="H16" t="n">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="I16" t="n">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="J16" t="n">
-        <v>972</v>
+        <v>1009</v>
       </c>
       <c r="K16" t="n">
-        <v>1240</v>
+        <v>984</v>
       </c>
       <c r="L16" t="n">
-        <v>1092.9</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>923</v>
+        <v>1092</v>
       </c>
       <c r="C17" t="n">
-        <v>1236</v>
+        <v>1057</v>
       </c>
       <c r="D17" t="n">
-        <v>1102</v>
+        <v>1072</v>
       </c>
       <c r="E17" t="n">
-        <v>1059</v>
+        <v>1143</v>
       </c>
       <c r="F17" t="n">
-        <v>963</v>
+        <v>1010</v>
       </c>
       <c r="G17" t="n">
-        <v>1253</v>
+        <v>1154</v>
       </c>
       <c r="H17" t="n">
-        <v>1101</v>
+        <v>998</v>
       </c>
       <c r="I17" t="n">
-        <v>1052</v>
+        <v>1146</v>
       </c>
       <c r="J17" t="n">
-        <v>1093</v>
+        <v>1213</v>
       </c>
       <c r="K17" t="n">
-        <v>1090</v>
+        <v>1076</v>
       </c>
       <c r="L17" t="n">
-        <v>1087.2</v>
+        <v>1096.1</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1022</v>
+        <v>974</v>
       </c>
       <c r="C18" t="n">
-        <v>1064</v>
+        <v>995</v>
       </c>
       <c r="D18" t="n">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="E18" t="n">
-        <v>1157</v>
+        <v>1019</v>
       </c>
       <c r="F18" t="n">
-        <v>1136</v>
+        <v>1080</v>
       </c>
       <c r="G18" t="n">
-        <v>1103</v>
+        <v>996</v>
       </c>
       <c r="H18" t="n">
-        <v>1069</v>
+        <v>1195</v>
       </c>
       <c r="I18" t="n">
-        <v>1007</v>
+        <v>1117</v>
       </c>
       <c r="J18" t="n">
-        <v>1137</v>
+        <v>1014</v>
       </c>
       <c r="K18" t="n">
-        <v>1138</v>
+        <v>1111</v>
       </c>
       <c r="L18" t="n">
-        <v>1091.2</v>
+        <v>1057.4</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1121</v>
+        <v>968</v>
       </c>
       <c r="C19" t="n">
-        <v>1069</v>
+        <v>1117</v>
       </c>
       <c r="D19" t="n">
-        <v>1110</v>
+        <v>1091</v>
       </c>
       <c r="E19" t="n">
-        <v>1268</v>
+        <v>1036</v>
       </c>
       <c r="F19" t="n">
+        <v>1192</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1161</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1094</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1118</v>
+      </c>
+      <c r="K19" t="n">
         <v>1078</v>
       </c>
-      <c r="G19" t="n">
-        <v>1082</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1216</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1105</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1218</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1122</v>
-      </c>
       <c r="L19" t="n">
-        <v>1138.9</v>
+        <v>1088.5</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1066</v>
+        <v>1381</v>
       </c>
       <c r="C20" t="n">
-        <v>1104</v>
+        <v>1085</v>
       </c>
       <c r="D20" t="n">
-        <v>1197</v>
+        <v>1034</v>
       </c>
       <c r="E20" t="n">
-        <v>1021</v>
+        <v>1293</v>
       </c>
       <c r="F20" t="n">
-        <v>972</v>
+        <v>1187</v>
       </c>
       <c r="G20" t="n">
-        <v>1072</v>
+        <v>1243</v>
       </c>
       <c r="H20" t="n">
-        <v>1067</v>
+        <v>1044</v>
       </c>
       <c r="I20" t="n">
-        <v>1342</v>
+        <v>1082</v>
       </c>
       <c r="J20" t="n">
-        <v>1048</v>
+        <v>1340</v>
       </c>
       <c r="K20" t="n">
-        <v>1177</v>
+        <v>1426</v>
       </c>
       <c r="L20" t="n">
-        <v>1106.6</v>
+        <v>1211.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1263</v>
+        <v>1007</v>
       </c>
       <c r="C21" t="n">
-        <v>1090</v>
+        <v>1139</v>
       </c>
       <c r="D21" t="n">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="E21" t="n">
-        <v>1169</v>
+        <v>1101</v>
       </c>
       <c r="F21" t="n">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="G21" t="n">
-        <v>1238</v>
+        <v>1194</v>
       </c>
       <c r="H21" t="n">
-        <v>1109</v>
+        <v>1156</v>
       </c>
       <c r="I21" t="n">
-        <v>1208</v>
+        <v>1136</v>
       </c>
       <c r="J21" t="n">
-        <v>1111</v>
+        <v>1148</v>
       </c>
       <c r="K21" t="n">
-        <v>1125</v>
+        <v>1140</v>
       </c>
       <c r="L21" t="n">
-        <v>1149.5</v>
+        <v>1123.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1242</v>
+        <v>1125</v>
       </c>
       <c r="C22" t="n">
-        <v>1202</v>
+        <v>1151</v>
       </c>
       <c r="D22" t="n">
-        <v>1109</v>
+        <v>1240</v>
       </c>
       <c r="E22" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F22" t="n">
-        <v>1185</v>
+        <v>1168</v>
       </c>
       <c r="G22" t="n">
-        <v>1264</v>
+        <v>1278</v>
       </c>
       <c r="H22" t="n">
-        <v>1184</v>
+        <v>1117</v>
       </c>
       <c r="I22" t="n">
-        <v>1291</v>
+        <v>1245</v>
       </c>
       <c r="J22" t="n">
-        <v>1176</v>
+        <v>1258</v>
       </c>
       <c r="K22" t="n">
-        <v>1062</v>
+        <v>1145</v>
       </c>
       <c r="L22" t="n">
-        <v>1196.8</v>
+        <v>1197.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1016</v>
+        <v>1078</v>
       </c>
       <c r="C23" t="n">
-        <v>928</v>
+        <v>911</v>
       </c>
       <c r="D23" t="n">
-        <v>1054</v>
+        <v>999</v>
       </c>
       <c r="E23" t="n">
-        <v>1104</v>
+        <v>980</v>
       </c>
       <c r="F23" t="n">
-        <v>1196</v>
+        <v>969</v>
       </c>
       <c r="G23" t="n">
+        <v>1042</v>
+      </c>
+      <c r="H23" t="n">
+        <v>975</v>
+      </c>
+      <c r="I23" t="n">
+        <v>902</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1083</v>
+      </c>
+      <c r="K23" t="n">
         <v>1031</v>
       </c>
-      <c r="H23" t="n">
-        <v>910</v>
-      </c>
-      <c r="I23" t="n">
-        <v>950</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1098</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1104</v>
-      </c>
       <c r="L23" t="n">
-        <v>1039.1</v>
+        <v>997</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1328</v>
+        <v>1042</v>
       </c>
       <c r="C24" t="n">
-        <v>1094</v>
+        <v>1124</v>
       </c>
       <c r="D24" t="n">
-        <v>1065</v>
+        <v>1188</v>
       </c>
       <c r="E24" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F24" t="n">
         <v>1143</v>
       </c>
-      <c r="F24" t="n">
-        <v>1182</v>
-      </c>
       <c r="G24" t="n">
-        <v>1183</v>
+        <v>1048</v>
       </c>
       <c r="H24" t="n">
-        <v>985</v>
+        <v>1096</v>
       </c>
       <c r="I24" t="n">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="J24" t="n">
-        <v>1058</v>
+        <v>954</v>
       </c>
       <c r="K24" t="n">
-        <v>977</v>
+        <v>1098</v>
       </c>
       <c r="L24" t="n">
-        <v>1114.1</v>
+        <v>1083.9</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1039</v>
+        <v>1166</v>
       </c>
       <c r="C25" t="n">
-        <v>1130</v>
+        <v>1200</v>
       </c>
       <c r="D25" t="n">
-        <v>1094</v>
+        <v>1170</v>
       </c>
       <c r="E25" t="n">
-        <v>1300</v>
+        <v>1109</v>
       </c>
       <c r="F25" t="n">
-        <v>1157</v>
+        <v>1375</v>
       </c>
       <c r="G25" t="n">
-        <v>1077</v>
+        <v>1247</v>
       </c>
       <c r="H25" t="n">
-        <v>1044</v>
+        <v>1161</v>
       </c>
       <c r="I25" t="n">
-        <v>1134</v>
+        <v>1156</v>
       </c>
       <c r="J25" t="n">
-        <v>1141</v>
+        <v>1262</v>
       </c>
       <c r="K25" t="n">
-        <v>1244</v>
+        <v>1100</v>
       </c>
       <c r="L25" t="n">
-        <v>1136</v>
+        <v>1194.6</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1000</v>
+        <v>1207</v>
       </c>
       <c r="C26" t="n">
-        <v>1153</v>
+        <v>1126</v>
       </c>
       <c r="D26" t="n">
-        <v>1219</v>
+        <v>1130</v>
       </c>
       <c r="E26" t="n">
-        <v>987</v>
+        <v>1148</v>
       </c>
       <c r="F26" t="n">
-        <v>1180</v>
+        <v>1054</v>
       </c>
       <c r="G26" t="n">
-        <v>995</v>
+        <v>1209</v>
       </c>
       <c r="H26" t="n">
-        <v>1105</v>
+        <v>1271</v>
       </c>
       <c r="I26" t="n">
-        <v>1069</v>
+        <v>1166</v>
       </c>
       <c r="J26" t="n">
-        <v>918</v>
+        <v>1181</v>
       </c>
       <c r="K26" t="n">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="L26" t="n">
-        <v>1064.4</v>
+        <v>1151.8</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
+        <v>1407</v>
+      </c>
+      <c r="C27" t="n">
         <v>1193</v>
       </c>
-      <c r="C27" t="n">
-        <v>1073</v>
-      </c>
       <c r="D27" t="n">
-        <v>1110</v>
+        <v>1093</v>
       </c>
       <c r="E27" t="n">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="F27" t="n">
-        <v>1148</v>
+        <v>1129</v>
       </c>
       <c r="G27" t="n">
-        <v>998</v>
+        <v>1131</v>
       </c>
       <c r="H27" t="n">
-        <v>1113</v>
+        <v>1312</v>
       </c>
       <c r="I27" t="n">
-        <v>1031</v>
+        <v>1158</v>
       </c>
       <c r="J27" t="n">
-        <v>1222</v>
+        <v>1250</v>
       </c>
       <c r="K27" t="n">
-        <v>1324</v>
+        <v>1161</v>
       </c>
       <c r="L27" t="n">
-        <v>1139.7</v>
+        <v>1203.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1009</v>
+        <v>999</v>
       </c>
       <c r="C28" t="n">
-        <v>1132</v>
+        <v>975</v>
       </c>
       <c r="D28" t="n">
-        <v>1047</v>
+        <v>1091</v>
       </c>
       <c r="E28" t="n">
-        <v>1035</v>
+        <v>1000</v>
       </c>
       <c r="F28" t="n">
-        <v>1074</v>
+        <v>1208</v>
       </c>
       <c r="G28" t="n">
-        <v>1077</v>
+        <v>1063</v>
       </c>
       <c r="H28" t="n">
-        <v>1032</v>
+        <v>967</v>
       </c>
       <c r="I28" t="n">
-        <v>1102</v>
+        <v>1024</v>
       </c>
       <c r="J28" t="n">
-        <v>1068</v>
+        <v>1098</v>
       </c>
       <c r="K28" t="n">
-        <v>982</v>
+        <v>1119</v>
       </c>
       <c r="L28" t="n">
-        <v>1055.8</v>
+        <v>1054.4</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>958</v>
+        <v>1092</v>
       </c>
       <c r="C29" t="n">
-        <v>979</v>
+        <v>1205</v>
       </c>
       <c r="D29" t="n">
-        <v>935</v>
+        <v>1023</v>
       </c>
       <c r="E29" t="n">
-        <v>1086</v>
+        <v>1003</v>
       </c>
       <c r="F29" t="n">
-        <v>1034</v>
+        <v>1094</v>
       </c>
       <c r="G29" t="n">
-        <v>951</v>
+        <v>980</v>
       </c>
       <c r="H29" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="I29" t="n">
-        <v>1102</v>
+        <v>995</v>
       </c>
       <c r="J29" t="n">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="K29" t="n">
-        <v>1068</v>
+        <v>937</v>
       </c>
       <c r="L29" t="n">
-        <v>1024.1</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1143</v>
+        <v>1055</v>
       </c>
       <c r="C30" t="n">
-        <v>1145</v>
+        <v>1059</v>
       </c>
       <c r="D30" t="n">
-        <v>1151</v>
+        <v>970</v>
       </c>
       <c r="E30" t="n">
-        <v>1145</v>
+        <v>1122</v>
       </c>
       <c r="F30" t="n">
-        <v>977</v>
+        <v>1084</v>
       </c>
       <c r="G30" t="n">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="H30" t="n">
-        <v>1060</v>
+        <v>1148</v>
       </c>
       <c r="I30" t="n">
-        <v>979</v>
+        <v>1028</v>
       </c>
       <c r="J30" t="n">
-        <v>988</v>
+        <v>1133</v>
       </c>
       <c r="K30" t="n">
-        <v>1137</v>
+        <v>1049</v>
       </c>
       <c r="L30" t="n">
-        <v>1083.7</v>
+        <v>1075.4</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1164</v>
+        <v>1422</v>
       </c>
       <c r="C31" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D31" t="n">
         <v>1078</v>
       </c>
-      <c r="D31" t="n">
-        <v>1186</v>
-      </c>
       <c r="E31" t="n">
-        <v>1168</v>
+        <v>1122</v>
       </c>
       <c r="F31" t="n">
-        <v>1334</v>
+        <v>1114</v>
       </c>
       <c r="G31" t="n">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="H31" t="n">
-        <v>1459</v>
+        <v>1060</v>
       </c>
       <c r="I31" t="n">
-        <v>1183</v>
+        <v>1122</v>
       </c>
       <c r="J31" t="n">
-        <v>1218</v>
+        <v>1336</v>
       </c>
       <c r="K31" t="n">
-        <v>1014</v>
+        <v>1134</v>
       </c>
       <c r="L31" t="n">
-        <v>1184.9</v>
+        <v>1146.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>954</v>
+        <v>992</v>
       </c>
       <c r="C32" t="n">
-        <v>984</v>
+        <v>1038</v>
       </c>
       <c r="D32" t="n">
-        <v>982</v>
+        <v>952</v>
       </c>
       <c r="E32" t="n">
-        <v>979</v>
+        <v>1232</v>
       </c>
       <c r="F32" t="n">
-        <v>1030</v>
+        <v>1013</v>
       </c>
       <c r="G32" t="n">
-        <v>1116</v>
+        <v>956</v>
       </c>
       <c r="H32" t="n">
-        <v>1046</v>
+        <v>948</v>
       </c>
       <c r="I32" t="n">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="J32" t="n">
-        <v>933</v>
+        <v>1017</v>
       </c>
       <c r="K32" t="n">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="L32" t="n">
-        <v>994.6</v>
+        <v>1007.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>973</v>
+        <v>1136</v>
       </c>
       <c r="C33" t="n">
-        <v>1007</v>
+        <v>1122</v>
       </c>
       <c r="D33" t="n">
-        <v>1080</v>
+        <v>1114</v>
       </c>
       <c r="E33" t="n">
-        <v>1042</v>
+        <v>1081</v>
       </c>
       <c r="F33" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G33" t="n">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="H33" t="n">
-        <v>1026</v>
+        <v>1070</v>
       </c>
       <c r="I33" t="n">
-        <v>1195</v>
+        <v>1065</v>
       </c>
       <c r="J33" t="n">
-        <v>1033</v>
+        <v>1156</v>
       </c>
       <c r="K33" t="n">
-        <v>1192</v>
+        <v>1023</v>
       </c>
       <c r="L33" t="n">
-        <v>1070.4</v>
+        <v>1091.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1184</v>
+        <v>1160</v>
       </c>
       <c r="C34" t="n">
-        <v>1234</v>
+        <v>1077</v>
       </c>
       <c r="D34" t="n">
-        <v>1090</v>
+        <v>1488</v>
       </c>
       <c r="E34" t="n">
-        <v>1114</v>
+        <v>1424</v>
       </c>
       <c r="F34" t="n">
-        <v>1148</v>
+        <v>1165</v>
       </c>
       <c r="G34" t="n">
-        <v>1050</v>
+        <v>1111</v>
       </c>
       <c r="H34" t="n">
-        <v>1079</v>
+        <v>1154</v>
       </c>
       <c r="I34" t="n">
-        <v>1015</v>
+        <v>1178</v>
       </c>
       <c r="J34" t="n">
-        <v>937</v>
+        <v>1237</v>
       </c>
       <c r="K34" t="n">
-        <v>1107</v>
+        <v>1406</v>
       </c>
       <c r="L34" t="n">
-        <v>1095.8</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1191</v>
+        <v>1015</v>
       </c>
       <c r="C35" t="n">
-        <v>1138</v>
+        <v>1118</v>
       </c>
       <c r="D35" t="n">
-        <v>1147</v>
+        <v>1043</v>
       </c>
       <c r="E35" t="n">
-        <v>1128</v>
+        <v>1064</v>
       </c>
       <c r="F35" t="n">
-        <v>1082</v>
+        <v>1104</v>
       </c>
       <c r="G35" t="n">
-        <v>1024</v>
+        <v>1058</v>
       </c>
       <c r="H35" t="n">
-        <v>1122</v>
+        <v>1171</v>
       </c>
       <c r="I35" t="n">
-        <v>1028</v>
+        <v>1093</v>
       </c>
       <c r="J35" t="n">
-        <v>1050</v>
+        <v>1181</v>
       </c>
       <c r="K35" t="n">
-        <v>1027</v>
+        <v>1087</v>
       </c>
       <c r="L35" t="n">
-        <v>1093.7</v>
+        <v>1093.4</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1047</v>
+        <v>1109</v>
       </c>
       <c r="C36" t="n">
-        <v>1125</v>
+        <v>1083</v>
       </c>
       <c r="D36" t="n">
-        <v>1146</v>
+        <v>1040</v>
       </c>
       <c r="E36" t="n">
-        <v>934</v>
+        <v>1170</v>
       </c>
       <c r="F36" t="n">
-        <v>1169</v>
+        <v>1089</v>
       </c>
       <c r="G36" t="n">
-        <v>1047</v>
+        <v>1097</v>
       </c>
       <c r="H36" t="n">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="I36" t="n">
-        <v>1089</v>
+        <v>1246</v>
       </c>
       <c r="J36" t="n">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="K36" t="n">
-        <v>1045</v>
+        <v>1106</v>
       </c>
       <c r="L36" t="n">
-        <v>1069.7</v>
+        <v>1104.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1052</v>
+        <v>1081</v>
       </c>
       <c r="C37" t="n">
-        <v>1161</v>
+        <v>1120</v>
       </c>
       <c r="D37" t="n">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="E37" t="n">
-        <v>1224</v>
+        <v>1159</v>
       </c>
       <c r="F37" t="n">
-        <v>1108</v>
+        <v>997</v>
       </c>
       <c r="G37" t="n">
+        <v>1066</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1145</v>
+      </c>
+      <c r="I37" t="n">
         <v>1130</v>
       </c>
-      <c r="H37" t="n">
-        <v>1087</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1146</v>
-      </c>
       <c r="J37" t="n">
-        <v>1047</v>
+        <v>1153</v>
       </c>
       <c r="K37" t="n">
-        <v>1304</v>
+        <v>1156</v>
       </c>
       <c r="L37" t="n">
-        <v>1136.1</v>
+        <v>1111.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1225</v>
+        <v>1053</v>
       </c>
       <c r="C38" t="n">
-        <v>1147</v>
+        <v>991</v>
       </c>
       <c r="D38" t="n">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="E38" t="n">
-        <v>955</v>
+        <v>1026</v>
       </c>
       <c r="F38" t="n">
         <v>1103</v>
       </c>
       <c r="G38" t="n">
-        <v>924</v>
+        <v>989</v>
       </c>
       <c r="H38" t="n">
-        <v>1249</v>
+        <v>915</v>
       </c>
       <c r="I38" t="n">
-        <v>1305</v>
+        <v>999</v>
       </c>
       <c r="J38" t="n">
-        <v>1058</v>
+        <v>1021</v>
       </c>
       <c r="K38" t="n">
-        <v>1196</v>
+        <v>993</v>
       </c>
       <c r="L38" t="n">
-        <v>1125.9</v>
+        <v>1018.2</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1059</v>
+        <v>1177</v>
       </c>
       <c r="C39" t="n">
-        <v>1045</v>
+        <v>1218</v>
       </c>
       <c r="D39" t="n">
-        <v>1054</v>
+        <v>1020</v>
       </c>
       <c r="E39" t="n">
-        <v>913</v>
+        <v>1112</v>
       </c>
       <c r="F39" t="n">
-        <v>1059</v>
+        <v>1089</v>
       </c>
       <c r="G39" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
       <c r="H39" t="n">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="I39" t="n">
-        <v>1202</v>
+        <v>991</v>
       </c>
       <c r="J39" t="n">
-        <v>1045</v>
+        <v>1078</v>
       </c>
       <c r="K39" t="n">
-        <v>981</v>
+        <v>1146</v>
       </c>
       <c r="L39" t="n">
-        <v>1036.6</v>
+        <v>1085.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1020</v>
+        <v>1115</v>
       </c>
       <c r="C40" t="n">
-        <v>1191</v>
+        <v>1225</v>
       </c>
       <c r="D40" t="n">
-        <v>1132</v>
+        <v>1077</v>
       </c>
       <c r="E40" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F40" t="n">
-        <v>1201</v>
+        <v>1053</v>
       </c>
       <c r="G40" t="n">
-        <v>1010</v>
+        <v>1206</v>
       </c>
       <c r="H40" t="n">
-        <v>1061</v>
+        <v>1113</v>
       </c>
       <c r="I40" t="n">
-        <v>1074</v>
+        <v>1200</v>
       </c>
       <c r="J40" t="n">
-        <v>1043</v>
+        <v>1208</v>
       </c>
       <c r="K40" t="n">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="L40" t="n">
-        <v>1087.5</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1018</v>
+        <v>1128</v>
       </c>
       <c r="C41" t="n">
-        <v>1189</v>
+        <v>1117</v>
       </c>
       <c r="D41" t="n">
-        <v>980</v>
+        <v>1153</v>
       </c>
       <c r="E41" t="n">
-        <v>1175</v>
+        <v>1069</v>
       </c>
       <c r="F41" t="n">
-        <v>1196</v>
+        <v>1072</v>
       </c>
       <c r="G41" t="n">
-        <v>918</v>
+        <v>1149</v>
       </c>
       <c r="H41" t="n">
-        <v>1063</v>
+        <v>1271</v>
       </c>
       <c r="I41" t="n">
-        <v>986</v>
+        <v>999</v>
       </c>
       <c r="J41" t="n">
-        <v>1024</v>
+        <v>1098</v>
       </c>
       <c r="K41" t="n">
-        <v>1013</v>
+        <v>1088</v>
       </c>
       <c r="L41" t="n">
-        <v>1056.2</v>
+        <v>1114.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>997</v>
+        <v>1070</v>
       </c>
       <c r="C42" t="n">
-        <v>1069</v>
+        <v>1127</v>
       </c>
       <c r="D42" t="n">
-        <v>1288</v>
+        <v>1136</v>
       </c>
       <c r="E42" t="n">
-        <v>1010</v>
+        <v>903</v>
       </c>
       <c r="F42" t="n">
-        <v>1168</v>
+        <v>990</v>
       </c>
       <c r="G42" t="n">
-        <v>1008</v>
+        <v>1223</v>
       </c>
       <c r="H42" t="n">
-        <v>1090</v>
+        <v>1128</v>
       </c>
       <c r="I42" t="n">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="J42" t="n">
-        <v>1009</v>
+        <v>987</v>
       </c>
       <c r="K42" t="n">
-        <v>988</v>
+        <v>1164</v>
       </c>
       <c r="L42" t="n">
-        <v>1059.7</v>
+        <v>1069.1</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1165</v>
+        <v>1238</v>
       </c>
       <c r="C43" t="n">
-        <v>1143</v>
+        <v>1107</v>
       </c>
       <c r="D43" t="n">
-        <v>1078</v>
+        <v>1167</v>
       </c>
       <c r="E43" t="n">
-        <v>1398</v>
+        <v>1347</v>
       </c>
       <c r="F43" t="n">
-        <v>1061</v>
+        <v>1093</v>
       </c>
       <c r="G43" t="n">
-        <v>1046</v>
+        <v>1131</v>
       </c>
       <c r="H43" t="n">
-        <v>1239</v>
+        <v>1084</v>
       </c>
       <c r="I43" t="n">
-        <v>1232</v>
+        <v>943</v>
       </c>
       <c r="J43" t="n">
         <v>1082</v>
       </c>
       <c r="K43" t="n">
-        <v>1069</v>
+        <v>993</v>
       </c>
       <c r="L43" t="n">
-        <v>1151.3</v>
+        <v>1118.5</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1121</v>
+      </c>
+      <c r="D44" t="n">
         <v>1141</v>
       </c>
-      <c r="C44" t="n">
-        <v>1131</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1031</v>
-      </c>
       <c r="E44" t="n">
-        <v>1083</v>
+        <v>1129</v>
       </c>
       <c r="F44" t="n">
-        <v>1189</v>
+        <v>994</v>
       </c>
       <c r="G44" t="n">
-        <v>1050</v>
+        <v>1207</v>
       </c>
       <c r="H44" t="n">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="I44" t="n">
-        <v>1051</v>
+        <v>1090</v>
       </c>
       <c r="J44" t="n">
-        <v>1065</v>
+        <v>1057</v>
       </c>
       <c r="K44" t="n">
-        <v>1096</v>
+        <v>1137</v>
       </c>
       <c r="L44" t="n">
-        <v>1093.5</v>
+        <v>1102.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1077</v>
+        <v>978</v>
       </c>
       <c r="C45" t="n">
-        <v>1049</v>
+        <v>1165</v>
       </c>
       <c r="D45" t="n">
-        <v>1075</v>
+        <v>939</v>
       </c>
       <c r="E45" t="n">
-        <v>1224</v>
+        <v>946</v>
       </c>
       <c r="F45" t="n">
-        <v>1132</v>
+        <v>1013</v>
       </c>
       <c r="G45" t="n">
-        <v>1048</v>
+        <v>925</v>
       </c>
       <c r="H45" t="n">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I45" t="n">
-        <v>1089</v>
+        <v>1150</v>
       </c>
       <c r="J45" t="n">
-        <v>1028</v>
+        <v>1046</v>
       </c>
       <c r="K45" t="n">
-        <v>1073</v>
+        <v>1179</v>
       </c>
       <c r="L45" t="n">
-        <v>1081.1</v>
+        <v>1035.8</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>944</v>
+        <v>1236</v>
       </c>
       <c r="C46" t="n">
-        <v>1240</v>
+        <v>1074</v>
       </c>
       <c r="D46" t="n">
-        <v>1147</v>
+        <v>1137</v>
       </c>
       <c r="E46" t="n">
-        <v>1190</v>
+        <v>1170</v>
       </c>
       <c r="F46" t="n">
-        <v>1059</v>
+        <v>1078</v>
       </c>
       <c r="G46" t="n">
-        <v>1153</v>
+        <v>1214</v>
       </c>
       <c r="H46" t="n">
-        <v>1164</v>
+        <v>1133</v>
       </c>
       <c r="I46" t="n">
-        <v>1074</v>
+        <v>1023</v>
       </c>
       <c r="J46" t="n">
-        <v>1253</v>
+        <v>1098</v>
       </c>
       <c r="K46" t="n">
-        <v>1136</v>
+        <v>1222</v>
       </c>
       <c r="L46" t="n">
-        <v>1136</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1054</v>
+        <v>1115</v>
       </c>
       <c r="C47" t="n">
-        <v>1107</v>
+        <v>1133</v>
       </c>
       <c r="D47" t="n">
-        <v>1070</v>
+        <v>1134</v>
       </c>
       <c r="E47" t="n">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="F47" t="n">
-        <v>1206</v>
+        <v>1056</v>
       </c>
       <c r="G47" t="n">
-        <v>1244</v>
+        <v>1101</v>
       </c>
       <c r="H47" t="n">
-        <v>1048</v>
+        <v>1292</v>
       </c>
       <c r="I47" t="n">
-        <v>1108</v>
+        <v>1217</v>
       </c>
       <c r="J47" t="n">
-        <v>1222</v>
+        <v>1098</v>
       </c>
       <c r="K47" t="n">
-        <v>1129</v>
+        <v>1146</v>
       </c>
       <c r="L47" t="n">
-        <v>1136.7</v>
+        <v>1146.4</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1027</v>
+        <v>983</v>
       </c>
       <c r="C48" t="n">
-        <v>1163</v>
+        <v>1039</v>
       </c>
       <c r="D48" t="n">
-        <v>982</v>
+        <v>1025</v>
       </c>
       <c r="E48" t="n">
-        <v>968</v>
+        <v>1114</v>
       </c>
       <c r="F48" t="n">
-        <v>1173</v>
+        <v>1068</v>
       </c>
       <c r="G48" t="n">
-        <v>1173</v>
+        <v>1242</v>
       </c>
       <c r="H48" t="n">
-        <v>1082</v>
+        <v>1145</v>
       </c>
       <c r="I48" t="n">
-        <v>1147</v>
+        <v>1078</v>
       </c>
       <c r="J48" t="n">
-        <v>1197</v>
+        <v>954</v>
       </c>
       <c r="K48" t="n">
-        <v>1302</v>
+        <v>1076</v>
       </c>
       <c r="L48" t="n">
-        <v>1121.4</v>
+        <v>1072.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1103</v>
+        <v>1128</v>
       </c>
       <c r="C49" t="n">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="D49" t="n">
-        <v>1206</v>
+        <v>1089</v>
       </c>
       <c r="E49" t="n">
-        <v>1046</v>
+        <v>980</v>
       </c>
       <c r="F49" t="n">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G49" t="n">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="H49" t="n">
-        <v>1024</v>
+        <v>1208</v>
       </c>
       <c r="I49" t="n">
-        <v>932</v>
+        <v>1091</v>
       </c>
       <c r="J49" t="n">
-        <v>1034</v>
+        <v>1111</v>
       </c>
       <c r="K49" t="n">
-        <v>1076</v>
+        <v>1091</v>
       </c>
       <c r="L49" t="n">
-        <v>1074</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1099</v>
+        <v>963</v>
       </c>
       <c r="C50" t="n">
-        <v>1222</v>
+        <v>1065</v>
       </c>
       <c r="D50" t="n">
-        <v>977</v>
+        <v>1028</v>
       </c>
       <c r="E50" t="n">
-        <v>941</v>
+        <v>980</v>
       </c>
       <c r="F50" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G50" t="n">
+        <v>916</v>
+      </c>
+      <c r="H50" t="n">
+        <v>976</v>
+      </c>
+      <c r="I50" t="n">
+        <v>942</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1081</v>
+      </c>
+      <c r="K50" t="n">
         <v>1063</v>
       </c>
-      <c r="G50" t="n">
-        <v>1059</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1003</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1050</v>
-      </c>
-      <c r="J50" t="n">
-        <v>994</v>
-      </c>
-      <c r="K50" t="n">
-        <v>926</v>
-      </c>
       <c r="L50" t="n">
-        <v>1033.4</v>
+        <v>1002.9</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="C51" t="n">
-        <v>1038</v>
+        <v>912</v>
       </c>
       <c r="D51" t="n">
-        <v>1010</v>
+        <v>982</v>
       </c>
       <c r="E51" t="n">
-        <v>1022</v>
+        <v>958</v>
       </c>
       <c r="F51" t="n">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="G51" t="n">
-        <v>1106</v>
+        <v>974</v>
       </c>
       <c r="H51" t="n">
-        <v>1121</v>
+        <v>975</v>
       </c>
       <c r="I51" t="n">
-        <v>1094</v>
+        <v>1063</v>
       </c>
       <c r="J51" t="n">
-        <v>1141</v>
+        <v>1107</v>
       </c>
       <c r="K51" t="n">
-        <v>1123</v>
+        <v>1080</v>
       </c>
       <c r="L51" t="n">
-        <v>1060.8</v>
+        <v>1002.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1073.62</v>
+        <v>1091.16</v>
       </c>
       <c r="C52" t="n">
-        <v>1090.4</v>
+        <v>1092.58</v>
       </c>
       <c r="D52" t="n">
-        <v>1081.16</v>
+        <v>1090.12</v>
       </c>
       <c r="E52" t="n">
-        <v>1108.88</v>
+        <v>1102.44</v>
       </c>
       <c r="F52" t="n">
-        <v>1104.58</v>
+        <v>1081.28</v>
       </c>
       <c r="G52" t="n">
-        <v>1085.64</v>
+        <v>1103.72</v>
       </c>
       <c r="H52" t="n">
-        <v>1090.36</v>
+        <v>1094.62</v>
       </c>
       <c r="I52" t="n">
-        <v>1089.36</v>
+        <v>1080.36</v>
       </c>
       <c r="J52" t="n">
-        <v>1078.6</v>
+        <v>1101.16</v>
       </c>
       <c r="K52" t="n">
-        <v>1100.96</v>
+        <v>1110.68</v>
       </c>
       <c r="L52" t="n">
-        <v>1090.356</v>
+        <v>1094.812</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>13.09472155570984</v>
+        <v>13.42924499511719</v>
       </c>
       <c r="C2" t="n">
-        <v>12.8718044757843</v>
+        <v>11.2168390750885</v>
       </c>
       <c r="D2" t="n">
-        <v>11.51520228385925</v>
+        <v>12.07714414596558</v>
       </c>
       <c r="E2" t="n">
-        <v>11.81647038459778</v>
+        <v>12.81168651580811</v>
       </c>
       <c r="F2" t="n">
-        <v>11.97751593589783</v>
+        <v>11.40085816383362</v>
       </c>
       <c r="G2" t="n">
-        <v>13.14305996894836</v>
+        <v>11.85569548606873</v>
       </c>
       <c r="H2" t="n">
-        <v>12.08877849578857</v>
+        <v>12.74435663223267</v>
       </c>
       <c r="I2" t="n">
-        <v>12.00795078277588</v>
+        <v>12.50699496269226</v>
       </c>
       <c r="J2" t="n">
-        <v>11.21250247955322</v>
+        <v>11.64974069595337</v>
       </c>
       <c r="K2" t="n">
-        <v>12.1591637134552</v>
+        <v>11.49610090255737</v>
       </c>
       <c r="L2" t="n">
-        <v>12.18871700763702</v>
+        <v>12.11886615753174</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>11.68127751350403</v>
+        <v>10.66026520729065</v>
       </c>
       <c r="C3" t="n">
-        <v>10.08685803413391</v>
+        <v>11.19300103187561</v>
       </c>
       <c r="D3" t="n">
-        <v>11.44289755821228</v>
+        <v>13.3319034576416</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03738331794739</v>
+        <v>10.93209862709045</v>
       </c>
       <c r="F3" t="n">
-        <v>11.46530771255493</v>
+        <v>11.76898074150085</v>
       </c>
       <c r="G3" t="n">
-        <v>12.01096343994141</v>
+        <v>13.08956813812256</v>
       </c>
       <c r="H3" t="n">
-        <v>11.6618709564209</v>
+        <v>11.04639291763306</v>
       </c>
       <c r="I3" t="n">
-        <v>11.72967195510864</v>
+        <v>11.87011337280273</v>
       </c>
       <c r="J3" t="n">
-        <v>10.54670810699463</v>
+        <v>11.96796345710754</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0294075012207</v>
+        <v>11.59043025970459</v>
       </c>
       <c r="L3" t="n">
-        <v>11.46923460960388</v>
+        <v>11.74507172107696</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>14.3735044002533</v>
+        <v>15.02943825721741</v>
       </c>
       <c r="C4" t="n">
-        <v>14.69462013244629</v>
+        <v>11.6208119392395</v>
       </c>
       <c r="D4" t="n">
-        <v>13.50115323066711</v>
+        <v>12.67160105705261</v>
       </c>
       <c r="E4" t="n">
-        <v>12.2508556842804</v>
+        <v>13.32389402389526</v>
       </c>
       <c r="F4" t="n">
-        <v>11.13618636131287</v>
+        <v>12.67502951622009</v>
       </c>
       <c r="G4" t="n">
-        <v>13.15109372138977</v>
+        <v>12.3304431438446</v>
       </c>
       <c r="H4" t="n">
-        <v>12.25240302085876</v>
+        <v>12.91794371604919</v>
       </c>
       <c r="I4" t="n">
-        <v>12.68770551681519</v>
+        <v>12.44669532775879</v>
       </c>
       <c r="J4" t="n">
-        <v>13.10614633560181</v>
+        <v>11.56892681121826</v>
       </c>
       <c r="K4" t="n">
-        <v>11.9111807346344</v>
+        <v>13.63358020782471</v>
       </c>
       <c r="L4" t="n">
-        <v>12.90648491382599</v>
+        <v>12.82183640003204</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>11.1680965423584</v>
+        <v>10.79701089859009</v>
       </c>
       <c r="C5" t="n">
-        <v>11.04140734672546</v>
+        <v>10.66333532333374</v>
       </c>
       <c r="D5" t="n">
-        <v>12.47471284866333</v>
+        <v>10.99951362609863</v>
       </c>
       <c r="E5" t="n">
-        <v>10.45641922950745</v>
+        <v>10.62241983413696</v>
       </c>
       <c r="F5" t="n">
-        <v>11.91232848167419</v>
+        <v>10.65228509902954</v>
       </c>
       <c r="G5" t="n">
-        <v>11.97756361961365</v>
+        <v>11.4393002986908</v>
       </c>
       <c r="H5" t="n">
-        <v>11.67031264305115</v>
+        <v>10.5490894317627</v>
       </c>
       <c r="I5" t="n">
-        <v>10.39657759666443</v>
+        <v>10.66181397438049</v>
       </c>
       <c r="J5" t="n">
-        <v>11.61250734329224</v>
+        <v>10.67767095565796</v>
       </c>
       <c r="K5" t="n">
-        <v>14.97238969802856</v>
+        <v>10.98744320869446</v>
       </c>
       <c r="L5" t="n">
-        <v>11.76823153495789</v>
+        <v>10.80498826503754</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>10.64396452903748</v>
+        <v>11.23379707336426</v>
       </c>
       <c r="C6" t="n">
-        <v>11.46137595176697</v>
+        <v>13.02979350090027</v>
       </c>
       <c r="D6" t="n">
-        <v>13.51645541191101</v>
+        <v>11.62347197532654</v>
       </c>
       <c r="E6" t="n">
-        <v>11.27968621253967</v>
+        <v>12.47475099563599</v>
       </c>
       <c r="F6" t="n">
-        <v>11.56895422935486</v>
+        <v>11.795569896698</v>
       </c>
       <c r="G6" t="n">
-        <v>15.15919375419617</v>
+        <v>11.37806630134583</v>
       </c>
       <c r="H6" t="n">
-        <v>11.76797652244568</v>
+        <v>11.94408798217773</v>
       </c>
       <c r="I6" t="n">
-        <v>12.04371428489685</v>
+        <v>11.88328385353088</v>
       </c>
       <c r="J6" t="n">
-        <v>10.52121901512146</v>
+        <v>11.7706127166748</v>
       </c>
       <c r="K6" t="n">
-        <v>12.92191886901855</v>
+        <v>10.64491987228394</v>
       </c>
       <c r="L6" t="n">
-        <v>12.08844587802887</v>
+        <v>11.77783541679382</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>11.22584104537964</v>
+        <v>12.65828728675842</v>
       </c>
       <c r="C7" t="n">
-        <v>10.77859997749329</v>
+        <v>11.03691172599792</v>
       </c>
       <c r="D7" t="n">
-        <v>11.63477730751038</v>
+        <v>11.74958372116089</v>
       </c>
       <c r="E7" t="n">
-        <v>11.44430184364319</v>
+        <v>10.89179706573486</v>
       </c>
       <c r="F7" t="n">
-        <v>11.8163480758667</v>
+        <v>10.76710414886475</v>
       </c>
       <c r="G7" t="n">
-        <v>12.21931838989258</v>
+        <v>11.8129506111145</v>
       </c>
       <c r="H7" t="n">
-        <v>11.25880098342896</v>
+        <v>15.35338354110718</v>
       </c>
       <c r="I7" t="n">
-        <v>12.06693696975708</v>
+        <v>11.554114818573</v>
       </c>
       <c r="J7" t="n">
-        <v>11.65933227539062</v>
+        <v>13.21550750732422</v>
       </c>
       <c r="K7" t="n">
-        <v>12.87076926231384</v>
+        <v>11.24936866760254</v>
       </c>
       <c r="L7" t="n">
-        <v>11.69750261306763</v>
+        <v>12.02890090942383</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>12.5257556438446</v>
+        <v>11.32765412330627</v>
       </c>
       <c r="C8" t="n">
-        <v>12.40697050094604</v>
+        <v>14.69457340240479</v>
       </c>
       <c r="D8" t="n">
-        <v>11.58093166351318</v>
+        <v>11.35313057899475</v>
       </c>
       <c r="E8" t="n">
-        <v>11.75596070289612</v>
+        <v>11.22545003890991</v>
       </c>
       <c r="F8" t="n">
-        <v>10.95257306098938</v>
+        <v>11.68726396560669</v>
       </c>
       <c r="G8" t="n">
-        <v>11.51708388328552</v>
+        <v>13.47925472259521</v>
       </c>
       <c r="H8" t="n">
-        <v>11.53407192230225</v>
+        <v>11.87874937057495</v>
       </c>
       <c r="I8" t="n">
-        <v>11.96042037010193</v>
+        <v>11.13015794754028</v>
       </c>
       <c r="J8" t="n">
-        <v>11.54682016372681</v>
+        <v>12.01169753074646</v>
       </c>
       <c r="K8" t="n">
-        <v>10.57413148880005</v>
+        <v>14.1325147151947</v>
       </c>
       <c r="L8" t="n">
-        <v>11.63547194004059</v>
+        <v>12.2920446395874</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>11.11811709403992</v>
+        <v>11.06533622741699</v>
       </c>
       <c r="C9" t="n">
-        <v>12.72618508338928</v>
+        <v>11.54414415359497</v>
       </c>
       <c r="D9" t="n">
-        <v>11.74361228942871</v>
+        <v>10.91573309898376</v>
       </c>
       <c r="E9" t="n">
-        <v>11.05791139602661</v>
+        <v>12.23286390304565</v>
       </c>
       <c r="F9" t="n">
-        <v>10.73824691772461</v>
+        <v>11.05686664581299</v>
       </c>
       <c r="G9" t="n">
-        <v>11.74161577224731</v>
+        <v>12.58047890663147</v>
       </c>
       <c r="H9" t="n">
-        <v>11.60845279693604</v>
+        <v>10.58209919929504</v>
       </c>
       <c r="I9" t="n">
-        <v>11.2678587436676</v>
+        <v>10.81845927238464</v>
       </c>
       <c r="J9" t="n">
-        <v>14.3440272808075</v>
+        <v>10.85504150390625</v>
       </c>
       <c r="K9" t="n">
-        <v>11.52321314811707</v>
+        <v>11.17054724693298</v>
       </c>
       <c r="L9" t="n">
-        <v>11.78692405223847</v>
+        <v>11.28215701580048</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>11.02155876159668</v>
+        <v>10.96062231063843</v>
       </c>
       <c r="C10" t="n">
-        <v>11.93066549301147</v>
+        <v>12.58401942253113</v>
       </c>
       <c r="D10" t="n">
-        <v>11.16014122962952</v>
+        <v>14.40835952758789</v>
       </c>
       <c r="E10" t="n">
-        <v>12.03239059448242</v>
+        <v>12.0633659362793</v>
       </c>
       <c r="F10" t="n">
-        <v>11.11826729774475</v>
+        <v>12.40640139579773</v>
       </c>
       <c r="G10" t="n">
-        <v>11.91106200218201</v>
+        <v>12.07728672027588</v>
       </c>
       <c r="H10" t="n">
-        <v>11.79951763153076</v>
+        <v>11.50801539421082</v>
       </c>
       <c r="I10" t="n">
-        <v>11.27384090423584</v>
+        <v>13.48765516281128</v>
       </c>
       <c r="J10" t="n">
-        <v>12.75003957748413</v>
+        <v>11.84292364120483</v>
       </c>
       <c r="K10" t="n">
-        <v>11.39806580543518</v>
+        <v>14.58707213401794</v>
       </c>
       <c r="L10" t="n">
-        <v>11.63955492973328</v>
+        <v>12.59257216453552</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>11.80796647071838</v>
+        <v>13.03983426094055</v>
       </c>
       <c r="C11" t="n">
-        <v>11.77656602859497</v>
+        <v>12.15957450866699</v>
       </c>
       <c r="D11" t="n">
-        <v>12.77712559700012</v>
+        <v>12.48098111152649</v>
       </c>
       <c r="E11" t="n">
-        <v>11.74664783477783</v>
+        <v>12.64216208457947</v>
       </c>
       <c r="F11" t="n">
-        <v>12.0573308467865</v>
+        <v>12.90495824813843</v>
       </c>
       <c r="G11" t="n">
-        <v>11.68578243255615</v>
+        <v>12.27629733085632</v>
       </c>
       <c r="H11" t="n">
-        <v>12.78300309181213</v>
+        <v>11.85034418106079</v>
       </c>
       <c r="I11" t="n">
-        <v>13.17948126792908</v>
+        <v>11.73863673210144</v>
       </c>
       <c r="J11" t="n">
-        <v>12.59049558639526</v>
+        <v>11.83888936042786</v>
       </c>
       <c r="K11" t="n">
-        <v>12.51369380950928</v>
+        <v>14.79692769050598</v>
       </c>
       <c r="L11" t="n">
-        <v>12.29180929660797</v>
+        <v>12.57286055088043</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>12.1884925365448</v>
+        <v>12.32317495346069</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49130392074585</v>
+        <v>13.61187529563904</v>
       </c>
       <c r="D12" t="n">
-        <v>12.33611536026001</v>
+        <v>12.33916807174683</v>
       </c>
       <c r="E12" t="n">
-        <v>17.90537452697754</v>
+        <v>11.68673205375671</v>
       </c>
       <c r="F12" t="n">
-        <v>14.61470341682434</v>
+        <v>12.11469626426697</v>
       </c>
       <c r="G12" t="n">
-        <v>12.94161796569824</v>
+        <v>16.29948329925537</v>
       </c>
       <c r="H12" t="n">
-        <v>11.75759291648865</v>
+        <v>12.08373665809631</v>
       </c>
       <c r="I12" t="n">
-        <v>11.73568940162659</v>
+        <v>12.41044020652771</v>
       </c>
       <c r="J12" t="n">
-        <v>15.79586458206177</v>
+        <v>12.03037047386169</v>
       </c>
       <c r="K12" t="n">
-        <v>18.42218518257141</v>
+        <v>12.04534387588501</v>
       </c>
       <c r="L12" t="n">
-        <v>13.91889398097992</v>
+        <v>12.69450211524963</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>12.34413003921509</v>
+        <v>12.17103719711304</v>
       </c>
       <c r="C13" t="n">
-        <v>12.77652144432068</v>
+        <v>11.66222286224365</v>
       </c>
       <c r="D13" t="n">
-        <v>14.18649554252625</v>
+        <v>12.29258918762207</v>
       </c>
       <c r="E13" t="n">
-        <v>13.44659471511841</v>
+        <v>12.82465100288391</v>
       </c>
       <c r="F13" t="n">
-        <v>13.76576924324036</v>
+        <v>13.09494757652283</v>
       </c>
       <c r="G13" t="n">
-        <v>12.56485342979431</v>
+        <v>13.33782935142517</v>
       </c>
       <c r="H13" t="n">
-        <v>14.16623663902283</v>
+        <v>12.15241861343384</v>
       </c>
       <c r="I13" t="n">
-        <v>12.26810383796692</v>
+        <v>13.36091995239258</v>
       </c>
       <c r="J13" t="n">
-        <v>13.13638591766357</v>
+        <v>12.86226391792297</v>
       </c>
       <c r="K13" t="n">
-        <v>16.82626628875732</v>
+        <v>13.77996373176575</v>
       </c>
       <c r="L13" t="n">
-        <v>13.54813570976257</v>
+        <v>12.75388433933258</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67481398582458</v>
+        <v>11.6513729095459</v>
       </c>
       <c r="C14" t="n">
-        <v>11.78056931495667</v>
+        <v>12.35805606842041</v>
       </c>
       <c r="D14" t="n">
-        <v>12.03145432472229</v>
+        <v>11.70770978927612</v>
       </c>
       <c r="E14" t="n">
-        <v>17.46270489692688</v>
+        <v>12.73510503768921</v>
       </c>
       <c r="F14" t="n">
-        <v>12.71683764457703</v>
+        <v>12.08576464653015</v>
       </c>
       <c r="G14" t="n">
-        <v>12.01643228530884</v>
+        <v>12.27672982215881</v>
       </c>
       <c r="H14" t="n">
-        <v>11.62245845794678</v>
+        <v>12.09576654434204</v>
       </c>
       <c r="I14" t="n">
-        <v>16.77086281776428</v>
+        <v>13.09887075424194</v>
       </c>
       <c r="J14" t="n">
-        <v>13.64976811408997</v>
+        <v>11.76394057273865</v>
       </c>
       <c r="K14" t="n">
-        <v>13.39275479316711</v>
+        <v>14.35824131965637</v>
       </c>
       <c r="L14" t="n">
-        <v>13.31186566352844</v>
+        <v>12.41315574645996</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>11.46939635276794</v>
+        <v>11.60688710212708</v>
       </c>
       <c r="C15" t="n">
-        <v>11.80798172950745</v>
+        <v>18.54917860031128</v>
       </c>
       <c r="D15" t="n">
-        <v>10.97956919670105</v>
+        <v>10.50376749038696</v>
       </c>
       <c r="E15" t="n">
-        <v>11.16209745407104</v>
+        <v>11.77251100540161</v>
       </c>
       <c r="F15" t="n">
-        <v>10.90280079841614</v>
+        <v>11.01394057273865</v>
       </c>
       <c r="G15" t="n">
-        <v>11.83889245986938</v>
+        <v>11.2144992351532</v>
       </c>
       <c r="H15" t="n">
-        <v>13.22731518745422</v>
+        <v>13.95202875137329</v>
       </c>
       <c r="I15" t="n">
-        <v>11.66292023658752</v>
+        <v>11.96898245811462</v>
       </c>
       <c r="J15" t="n">
-        <v>11.41600680351257</v>
+        <v>10.9380738735199</v>
       </c>
       <c r="K15" t="n">
-        <v>11.1365978717804</v>
+        <v>11.64271187782288</v>
       </c>
       <c r="L15" t="n">
-        <v>11.56035780906677</v>
+        <v>12.31625809669495</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>12.56585669517517</v>
+        <v>12.59928703308105</v>
       </c>
       <c r="C16" t="n">
-        <v>11.22485280036926</v>
+        <v>11.96689629554749</v>
       </c>
       <c r="D16" t="n">
-        <v>11.99587917327881</v>
+        <v>12.32979083061218</v>
       </c>
       <c r="E16" t="n">
-        <v>16.5804226398468</v>
+        <v>11.23341083526611</v>
       </c>
       <c r="F16" t="n">
-        <v>12.99424648284912</v>
+        <v>11.55909371376038</v>
       </c>
       <c r="G16" t="n">
-        <v>12.61007452011108</v>
+        <v>11.98981785774231</v>
       </c>
       <c r="H16" t="n">
-        <v>12.55852627754211</v>
+        <v>12.15856242179871</v>
       </c>
       <c r="I16" t="n">
-        <v>11.46422433853149</v>
+        <v>11.91715312004089</v>
       </c>
       <c r="J16" t="n">
-        <v>11.51561450958252</v>
+        <v>11.82592940330505</v>
       </c>
       <c r="K16" t="n">
-        <v>15.43891763687134</v>
+        <v>11.75458431243896</v>
       </c>
       <c r="L16" t="n">
-        <v>12.89486150741577</v>
+        <v>11.93345258235931</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>11.12306547164917</v>
+        <v>10.87889003753662</v>
       </c>
       <c r="C17" t="n">
-        <v>13.99241089820862</v>
+        <v>12.74906539916992</v>
       </c>
       <c r="D17" t="n">
-        <v>11.67979788780212</v>
+        <v>10.80168628692627</v>
       </c>
       <c r="E17" t="n">
-        <v>11.99097967147827</v>
+        <v>11.88875484466553</v>
       </c>
       <c r="F17" t="n">
-        <v>11.49451279640198</v>
+        <v>10.55914068222046</v>
       </c>
       <c r="G17" t="n">
-        <v>12.3022620677948</v>
+        <v>10.97558665275574</v>
       </c>
       <c r="H17" t="n">
-        <v>12.67471861839294</v>
+        <v>11.58355641365051</v>
       </c>
       <c r="I17" t="n">
-        <v>12.00849938392639</v>
+        <v>12.51011991500854</v>
       </c>
       <c r="J17" t="n">
-        <v>12.40045189857483</v>
+        <v>13.15951228141785</v>
       </c>
       <c r="K17" t="n">
-        <v>11.48080492019653</v>
+        <v>11.38656783103943</v>
       </c>
       <c r="L17" t="n">
-        <v>12.11475036144257</v>
+        <v>11.64928803443909</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>11.50423741340637</v>
+        <v>11.48728656768799</v>
       </c>
       <c r="C18" t="n">
-        <v>12.87525582313538</v>
+        <v>11.46088051795959</v>
       </c>
       <c r="D18" t="n">
-        <v>12.36557102203369</v>
+        <v>11.87626624107361</v>
       </c>
       <c r="E18" t="n">
-        <v>12.08627033233643</v>
+        <v>11.80099368095398</v>
       </c>
       <c r="F18" t="n">
-        <v>12.31318998336792</v>
+        <v>11.79248666763306</v>
       </c>
       <c r="G18" t="n">
-        <v>12.45933151245117</v>
+        <v>11.57658100128174</v>
       </c>
       <c r="H18" t="n">
-        <v>11.99447560310364</v>
+        <v>12.48422718048096</v>
       </c>
       <c r="I18" t="n">
-        <v>11.9722158908844</v>
+        <v>12.65432143211365</v>
       </c>
       <c r="J18" t="n">
-        <v>14.43528604507446</v>
+        <v>11.77252411842346</v>
       </c>
       <c r="K18" t="n">
-        <v>11.9526219367981</v>
+        <v>12.42372608184814</v>
       </c>
       <c r="L18" t="n">
-        <v>12.39584555625916</v>
+        <v>11.93292934894562</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>11.60346984863281</v>
+        <v>11.5815691947937</v>
       </c>
       <c r="C19" t="n">
-        <v>11.62748503684998</v>
+        <v>11.50520420074463</v>
       </c>
       <c r="D19" t="n">
-        <v>11.56505751609802</v>
+        <v>11.60595202445984</v>
       </c>
       <c r="E19" t="n">
-        <v>12.55558395385742</v>
+        <v>11.77705836296082</v>
       </c>
       <c r="F19" t="n">
-        <v>12.93561220169067</v>
+        <v>11.33424496650696</v>
       </c>
       <c r="G19" t="n">
-        <v>11.69475913047791</v>
+        <v>10.90277314186096</v>
       </c>
       <c r="H19" t="n">
-        <v>16.17234301567078</v>
+        <v>11.05386972427368</v>
       </c>
       <c r="I19" t="n">
-        <v>12.21794772148132</v>
+        <v>11.19054102897644</v>
       </c>
       <c r="J19" t="n">
-        <v>12.14775347709656</v>
+        <v>11.55463361740112</v>
       </c>
       <c r="K19" t="n">
-        <v>12.47677659988403</v>
+        <v>11.52520990371704</v>
       </c>
       <c r="L19" t="n">
-        <v>12.49967885017395</v>
+        <v>11.40310561656952</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>10.98007607460022</v>
+        <v>14.88563823699951</v>
       </c>
       <c r="C20" t="n">
-        <v>10.63697719573975</v>
+        <v>11.45885586738586</v>
       </c>
       <c r="D20" t="n">
-        <v>12.33394837379456</v>
+        <v>11.44587802886963</v>
       </c>
       <c r="E20" t="n">
-        <v>10.27030277252197</v>
+        <v>14.68215751647949</v>
       </c>
       <c r="F20" t="n">
-        <v>10.64038491249084</v>
+        <v>12.83730101585388</v>
       </c>
       <c r="G20" t="n">
-        <v>11.77566957473755</v>
+        <v>15.25105404853821</v>
       </c>
       <c r="H20" t="n">
-        <v>12.54671144485474</v>
+        <v>11.42988181114197</v>
       </c>
       <c r="I20" t="n">
-        <v>13.56770610809326</v>
+        <v>11.08221173286438</v>
       </c>
       <c r="J20" t="n">
-        <v>10.92011451721191</v>
+        <v>16.09949088096619</v>
       </c>
       <c r="K20" t="n">
-        <v>12.85732698440552</v>
+        <v>16.01136541366577</v>
       </c>
       <c r="L20" t="n">
-        <v>11.65292179584503</v>
+        <v>13.51838345527649</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>11.82130575180054</v>
+        <v>11.17045116424561</v>
       </c>
       <c r="C21" t="n">
-        <v>11.66374158859253</v>
+        <v>11.6048572063446</v>
       </c>
       <c r="D21" t="n">
-        <v>11.57094764709473</v>
+        <v>10.87822580337524</v>
       </c>
       <c r="E21" t="n">
-        <v>11.26774859428406</v>
+        <v>11.0019223690033</v>
       </c>
       <c r="F21" t="n">
-        <v>12.36695241928101</v>
+        <v>11.13457608222961</v>
       </c>
       <c r="G21" t="n">
-        <v>11.1884777545929</v>
+        <v>12.97327089309692</v>
       </c>
       <c r="H21" t="n">
-        <v>11.20551133155823</v>
+        <v>13.12236499786377</v>
       </c>
       <c r="I21" t="n">
-        <v>14.15649199485779</v>
+        <v>12.11002540588379</v>
       </c>
       <c r="J21" t="n">
-        <v>11.15962934494019</v>
+        <v>10.81686973571777</v>
       </c>
       <c r="K21" t="n">
-        <v>12.13881516456604</v>
+        <v>12.43867659568787</v>
       </c>
       <c r="L21" t="n">
-        <v>11.8539621591568</v>
+        <v>11.72512402534485</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>13.82486581802368</v>
+        <v>11.77893996238708</v>
       </c>
       <c r="C22" t="n">
-        <v>13.66523122787476</v>
+        <v>12.08711338043213</v>
       </c>
       <c r="D22" t="n">
-        <v>12.31621289253235</v>
+        <v>12.21424150466919</v>
       </c>
       <c r="E22" t="n">
-        <v>12.37700653076172</v>
+        <v>12.37935185432434</v>
       </c>
       <c r="F22" t="n">
-        <v>12.98300123214722</v>
+        <v>12.50098896026611</v>
       </c>
       <c r="G22" t="n">
-        <v>12.26681399345398</v>
+        <v>12.93192386627197</v>
       </c>
       <c r="H22" t="n">
-        <v>12.56904172897339</v>
+        <v>11.5664267539978</v>
       </c>
       <c r="I22" t="n">
-        <v>13.56103205680847</v>
+        <v>12.75154852867126</v>
       </c>
       <c r="J22" t="n">
-        <v>11.85581493377686</v>
+        <v>13.13974761962891</v>
       </c>
       <c r="K22" t="n">
-        <v>11.8521773815155</v>
+        <v>11.14614534378052</v>
       </c>
       <c r="L22" t="n">
-        <v>12.72711977958679</v>
+        <v>12.24964277744293</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>11.11364769935608</v>
+        <v>12.4094500541687</v>
       </c>
       <c r="C23" t="n">
-        <v>10.86683106422424</v>
+        <v>10.86039590835571</v>
       </c>
       <c r="D23" t="n">
-        <v>11.70708513259888</v>
+        <v>10.66836714744568</v>
       </c>
       <c r="E23" t="n">
-        <v>11.48118138313293</v>
+        <v>10.72324132919312</v>
       </c>
       <c r="F23" t="n">
-        <v>14.43763089179993</v>
+        <v>9.571142435073853</v>
       </c>
       <c r="G23" t="n">
-        <v>11.74527859687805</v>
+        <v>9.937199592590332</v>
       </c>
       <c r="H23" t="n">
-        <v>11.23545622825623</v>
+        <v>10.28136372566223</v>
       </c>
       <c r="I23" t="n">
-        <v>11.42790341377258</v>
+        <v>10.06643795967102</v>
       </c>
       <c r="J23" t="n">
-        <v>11.46682929992676</v>
+        <v>11.7321982383728</v>
       </c>
       <c r="K23" t="n">
-        <v>10.89879941940308</v>
+        <v>12.05186772346497</v>
       </c>
       <c r="L23" t="n">
-        <v>11.63806431293488</v>
+        <v>10.83016641139984</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>14.18640351295471</v>
+        <v>11.16810131072998</v>
       </c>
       <c r="C24" t="n">
-        <v>12.48282670974731</v>
+        <v>11.83888363838196</v>
       </c>
       <c r="D24" t="n">
-        <v>11.70373725891113</v>
+        <v>13.2872908115387</v>
       </c>
       <c r="E24" t="n">
-        <v>12.10223913192749</v>
+        <v>11.47437715530396</v>
       </c>
       <c r="F24" t="n">
-        <v>11.9974946975708</v>
+        <v>11.74612808227539</v>
       </c>
       <c r="G24" t="n">
-        <v>12.70616412162781</v>
+        <v>11.68426895141602</v>
       </c>
       <c r="H24" t="n">
-        <v>12.56157398223877</v>
+        <v>11.80055809020996</v>
       </c>
       <c r="I24" t="n">
-        <v>13.89516854286194</v>
+        <v>11.58601808547974</v>
       </c>
       <c r="J24" t="n">
-        <v>13.61839079856873</v>
+        <v>11.86532330513</v>
       </c>
       <c r="K24" t="n">
-        <v>12.46332287788391</v>
+        <v>12.68475079536438</v>
       </c>
       <c r="L24" t="n">
-        <v>12.77173216342926</v>
+        <v>11.91357002258301</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>13.13017773628235</v>
+        <v>13.52577018737793</v>
       </c>
       <c r="C25" t="n">
-        <v>12.96157002449036</v>
+        <v>14.80025053024292</v>
       </c>
       <c r="D25" t="n">
-        <v>13.45572662353516</v>
+        <v>13.28471279144287</v>
       </c>
       <c r="E25" t="n">
-        <v>14.26474666595459</v>
+        <v>14.39194464683533</v>
       </c>
       <c r="F25" t="n">
-        <v>13.36552309989929</v>
+        <v>18.86798357963562</v>
       </c>
       <c r="G25" t="n">
-        <v>12.77247953414917</v>
+        <v>14.94600009918213</v>
       </c>
       <c r="H25" t="n">
-        <v>12.65980195999146</v>
+        <v>14.61133360862732</v>
       </c>
       <c r="I25" t="n">
-        <v>13.34557175636292</v>
+        <v>13.17748665809631</v>
       </c>
       <c r="J25" t="n">
-        <v>13.1635468006134</v>
+        <v>15.80028343200684</v>
       </c>
       <c r="K25" t="n">
-        <v>14.58044505119324</v>
+        <v>13.56451916694641</v>
       </c>
       <c r="L25" t="n">
-        <v>13.36995892524719</v>
+        <v>14.69702847003937</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>10.43528079986572</v>
+        <v>11.94813466072083</v>
       </c>
       <c r="C26" t="n">
-        <v>10.11776232719421</v>
+        <v>11.50127816200256</v>
       </c>
       <c r="D26" t="n">
-        <v>16.88269901275635</v>
+        <v>12.83636212348938</v>
       </c>
       <c r="E26" t="n">
-        <v>10.93509674072266</v>
+        <v>10.71230316162109</v>
       </c>
       <c r="F26" t="n">
-        <v>10.87625312805176</v>
+        <v>11.81132984161377</v>
       </c>
       <c r="G26" t="n">
-        <v>10.46499824523926</v>
+        <v>12.50249862670898</v>
       </c>
       <c r="H26" t="n">
-        <v>11.42197442054749</v>
+        <v>18.51365756988525</v>
       </c>
       <c r="I26" t="n">
-        <v>12.39516115188599</v>
+        <v>11.85421586036682</v>
       </c>
       <c r="J26" t="n">
-        <v>10.33866167068481</v>
+        <v>12.37629699707031</v>
       </c>
       <c r="K26" t="n">
-        <v>11.07179951667786</v>
+        <v>10.79654335975647</v>
       </c>
       <c r="L26" t="n">
-        <v>11.49396870136261</v>
+        <v>12.48526203632355</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>12.01085233688354</v>
+        <v>15.25764918327332</v>
       </c>
       <c r="C27" t="n">
-        <v>11.06706309318542</v>
+        <v>12.2538206577301</v>
       </c>
       <c r="D27" t="n">
-        <v>12.91556644439697</v>
+        <v>12.30720543861389</v>
       </c>
       <c r="E27" t="n">
-        <v>12.66459488868713</v>
+        <v>12.15057802200317</v>
       </c>
       <c r="F27" t="n">
-        <v>12.60672831535339</v>
+        <v>11.89074110984802</v>
       </c>
       <c r="G27" t="n">
-        <v>12.21227192878723</v>
+        <v>12.03739619255066</v>
       </c>
       <c r="H27" t="n">
-        <v>11.22584843635559</v>
+        <v>13.35353493690491</v>
       </c>
       <c r="I27" t="n">
-        <v>11.21438932418823</v>
+        <v>11.96803736686707</v>
       </c>
       <c r="J27" t="n">
-        <v>11.76856255531311</v>
+        <v>13.92008924484253</v>
       </c>
       <c r="K27" t="n">
-        <v>15.81729817390442</v>
+        <v>12.95056939125061</v>
       </c>
       <c r="L27" t="n">
-        <v>12.3503175497055</v>
+        <v>12.80896215438843</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>10.8055317401886</v>
+        <v>10.90575170516968</v>
       </c>
       <c r="C28" t="n">
-        <v>12.35010313987732</v>
+        <v>11.39801859855652</v>
       </c>
       <c r="D28" t="n">
-        <v>11.47279667854309</v>
+        <v>10.82646083831787</v>
       </c>
       <c r="E28" t="n">
-        <v>10.69527363777161</v>
+        <v>11.0019953250885</v>
       </c>
       <c r="F28" t="n">
-        <v>11.91344332695007</v>
+        <v>13.90365195274353</v>
       </c>
       <c r="G28" t="n">
-        <v>11.39851903915405</v>
+        <v>11.43092584609985</v>
       </c>
       <c r="H28" t="n">
-        <v>12.93460035324097</v>
+        <v>10.41351747512817</v>
       </c>
       <c r="I28" t="n">
-        <v>11.49379658699036</v>
+        <v>10.32127380371094</v>
       </c>
       <c r="J28" t="n">
-        <v>11.20702314376831</v>
+        <v>13.75702524185181</v>
       </c>
       <c r="K28" t="n">
-        <v>12.07365655899048</v>
+        <v>11.22945165634155</v>
       </c>
       <c r="L28" t="n">
-        <v>11.63447442054749</v>
+        <v>11.51880724430084</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>10.70921301841736</v>
+        <v>10.37109732627869</v>
       </c>
       <c r="C29" t="n">
-        <v>11.05875968933105</v>
+        <v>11.56155800819397</v>
       </c>
       <c r="D29" t="n">
-        <v>10.00360202789307</v>
+        <v>10.11282253265381</v>
       </c>
       <c r="E29" t="n">
-        <v>10.99792981147766</v>
+        <v>9.873331069946289</v>
       </c>
       <c r="F29" t="n">
-        <v>10.67877864837646</v>
+        <v>12.14697504043579</v>
       </c>
       <c r="G29" t="n">
-        <v>10.85594153404236</v>
+        <v>11.26268720626831</v>
       </c>
       <c r="H29" t="n">
-        <v>12.40682029724121</v>
+        <v>9.776643753051758</v>
       </c>
       <c r="I29" t="n">
-        <v>10.73462605476379</v>
+        <v>10.25292015075684</v>
       </c>
       <c r="J29" t="n">
-        <v>10.96898722648621</v>
+        <v>11.48825001716614</v>
       </c>
       <c r="K29" t="n">
-        <v>10.52912068367004</v>
+        <v>9.821211099624634</v>
       </c>
       <c r="L29" t="n">
-        <v>10.89437789916992</v>
+        <v>10.66674962043762</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>11.83730292320251</v>
+        <v>10.48682522773743</v>
       </c>
       <c r="C30" t="n">
-        <v>12.21624350547791</v>
+        <v>11.37652635574341</v>
       </c>
       <c r="D30" t="n">
-        <v>11.69363021850586</v>
+        <v>11.5301992893219</v>
       </c>
       <c r="E30" t="n">
-        <v>11.75346422195435</v>
+        <v>14.01234674453735</v>
       </c>
       <c r="F30" t="n">
-        <v>11.69863986968994</v>
+        <v>11.85577201843262</v>
       </c>
       <c r="G30" t="n">
-        <v>12.26518845558167</v>
+        <v>13.12229084968567</v>
       </c>
       <c r="H30" t="n">
-        <v>11.49173331260681</v>
+        <v>13.16481709480286</v>
       </c>
       <c r="I30" t="n">
-        <v>10.69174695014954</v>
+        <v>10.89964294433594</v>
       </c>
       <c r="J30" t="n">
-        <v>11.95746397972107</v>
+        <v>11.75942325592041</v>
       </c>
       <c r="K30" t="n">
-        <v>11.8452296257019</v>
+        <v>11.69563508033752</v>
       </c>
       <c r="L30" t="n">
-        <v>11.74506430625916</v>
+        <v>11.99034788608551</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>12.55497145652771</v>
+        <v>15.33367443084717</v>
       </c>
       <c r="C31" t="n">
-        <v>13.75951147079468</v>
+        <v>12.14402627944946</v>
       </c>
       <c r="D31" t="n">
-        <v>12.66729068756104</v>
+        <v>11.63877248764038</v>
       </c>
       <c r="E31" t="n">
-        <v>12.17854356765747</v>
+        <v>11.74798035621643</v>
       </c>
       <c r="F31" t="n">
-        <v>14.5175609588623</v>
+        <v>14.23505854606628</v>
       </c>
       <c r="G31" t="n">
-        <v>11.74466753005981</v>
+        <v>11.63482117652893</v>
       </c>
       <c r="H31" t="n">
-        <v>15.68037629127502</v>
+        <v>12.70844578742981</v>
       </c>
       <c r="I31" t="n">
-        <v>12.76428556442261</v>
+        <v>12.25817370414734</v>
       </c>
       <c r="J31" t="n">
-        <v>15.14716196060181</v>
+        <v>16.48266768455505</v>
       </c>
       <c r="K31" t="n">
-        <v>11.07973003387451</v>
+        <v>12.67104935646057</v>
       </c>
       <c r="L31" t="n">
-        <v>13.2094099521637</v>
+        <v>13.08546698093414</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>11.41743111610413</v>
+        <v>11.77639174461365</v>
       </c>
       <c r="C32" t="n">
-        <v>12.22283840179443</v>
+        <v>11.84962964057922</v>
       </c>
       <c r="D32" t="n">
-        <v>12.61990547180176</v>
+        <v>10.75361585617065</v>
       </c>
       <c r="E32" t="n">
-        <v>11.44887161254883</v>
+        <v>16.39641284942627</v>
       </c>
       <c r="F32" t="n">
-        <v>11.29529356956482</v>
+        <v>10.86974549293518</v>
       </c>
       <c r="G32" t="n">
-        <v>11.75477528572083</v>
+        <v>11.35946774482727</v>
       </c>
       <c r="H32" t="n">
-        <v>12.20433640480042</v>
+        <v>11.77400302886963</v>
       </c>
       <c r="I32" t="n">
-        <v>11.15952944755554</v>
+        <v>10.92809343338013</v>
       </c>
       <c r="J32" t="n">
-        <v>11.34301829338074</v>
+        <v>12.83967709541321</v>
       </c>
       <c r="K32" t="n">
-        <v>11.39038848876953</v>
+        <v>11.54059052467346</v>
       </c>
       <c r="L32" t="n">
-        <v>11.6856388092041</v>
+        <v>12.00876274108887</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>11.83231782913208</v>
+        <v>11.73096942901611</v>
       </c>
       <c r="C33" t="n">
-        <v>11.7739200592041</v>
+        <v>11.93750047683716</v>
       </c>
       <c r="D33" t="n">
-        <v>13.07554626464844</v>
+        <v>11.39635515213013</v>
       </c>
       <c r="E33" t="n">
-        <v>11.89312171936035</v>
+        <v>11.89607667922974</v>
       </c>
       <c r="F33" t="n">
-        <v>11.53002762794495</v>
+        <v>11.9609386920929</v>
       </c>
       <c r="G33" t="n">
-        <v>12.42024970054626</v>
+        <v>11.48915505409241</v>
       </c>
       <c r="H33" t="n">
-        <v>12.17602109909058</v>
+        <v>11.74399828910828</v>
       </c>
       <c r="I33" t="n">
-        <v>11.74962902069092</v>
+        <v>11.22087574005127</v>
       </c>
       <c r="J33" t="n">
-        <v>12.81944036483765</v>
+        <v>13.75823760032654</v>
       </c>
       <c r="K33" t="n">
-        <v>12.73012900352478</v>
+        <v>11.78785467147827</v>
       </c>
       <c r="L33" t="n">
-        <v>12.20004026889801</v>
+        <v>11.89219617843628</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>14.64479231834412</v>
+        <v>11.01437735557556</v>
       </c>
       <c r="C34" t="n">
-        <v>12.93558406829834</v>
+        <v>10.54611229896545</v>
       </c>
       <c r="D34" t="n">
-        <v>11.60256171226501</v>
+        <v>16.6520516872406</v>
       </c>
       <c r="E34" t="n">
-        <v>10.63693976402283</v>
+        <v>15.82270050048828</v>
       </c>
       <c r="F34" t="n">
-        <v>12.26135087013245</v>
+        <v>11.76525282859802</v>
       </c>
       <c r="G34" t="n">
-        <v>11.53923034667969</v>
+        <v>11.37016749382019</v>
       </c>
       <c r="H34" t="n">
-        <v>10.34716892242432</v>
+        <v>12.10325121879578</v>
       </c>
       <c r="I34" t="n">
-        <v>10.46438264846802</v>
+        <v>10.87583613395691</v>
       </c>
       <c r="J34" t="n">
-        <v>11.15759515762329</v>
+        <v>11.58454370498657</v>
       </c>
       <c r="K34" t="n">
-        <v>11.17110562324524</v>
+        <v>13.9621946811676</v>
       </c>
       <c r="L34" t="n">
-        <v>11.67607114315033</v>
+        <v>12.5696487903595</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>13.37802147865295</v>
+        <v>12.28370761871338</v>
       </c>
       <c r="C35" t="n">
-        <v>12.72512912750244</v>
+        <v>12.1750020980835</v>
       </c>
       <c r="D35" t="n">
-        <v>12.51766467094421</v>
+        <v>12.74539303779602</v>
       </c>
       <c r="E35" t="n">
-        <v>12.48719906806946</v>
+        <v>11.4558961391449</v>
       </c>
       <c r="F35" t="n">
-        <v>12.12169480323792</v>
+        <v>12.0841326713562</v>
       </c>
       <c r="G35" t="n">
-        <v>11.56539487838745</v>
+        <v>12.86311435699463</v>
       </c>
       <c r="H35" t="n">
-        <v>12.15160036087036</v>
+        <v>12.78746199607849</v>
       </c>
       <c r="I35" t="n">
-        <v>11.70472407341003</v>
+        <v>12.67972230911255</v>
       </c>
       <c r="J35" t="n">
-        <v>11.23840188980103</v>
+        <v>13.47176599502563</v>
       </c>
       <c r="K35" t="n">
-        <v>11.4054970741272</v>
+        <v>12.57500052452087</v>
       </c>
       <c r="L35" t="n">
-        <v>12.12953274250031</v>
+        <v>12.51211967468262</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>12.10924053192139</v>
+        <v>11.95407700538635</v>
       </c>
       <c r="C36" t="n">
-        <v>12.3665235042572</v>
+        <v>13.14003658294678</v>
       </c>
       <c r="D36" t="n">
-        <v>14.70463991165161</v>
+        <v>11.22546052932739</v>
       </c>
       <c r="E36" t="n">
-        <v>11.14169502258301</v>
+        <v>11.56256246566772</v>
       </c>
       <c r="F36" t="n">
-        <v>13.91259956359863</v>
+        <v>11.05788254737854</v>
       </c>
       <c r="G36" t="n">
-        <v>12.24634790420532</v>
+        <v>11.14220190048218</v>
       </c>
       <c r="H36" t="n">
-        <v>13.22236156463623</v>
+        <v>11.73964333534241</v>
       </c>
       <c r="I36" t="n">
-        <v>12.26088190078735</v>
+        <v>11.8613007068634</v>
       </c>
       <c r="J36" t="n">
-        <v>13.44993615150452</v>
+        <v>11.65140080451965</v>
       </c>
       <c r="K36" t="n">
-        <v>15.77862143516541</v>
+        <v>11.50522398948669</v>
       </c>
       <c r="L36" t="n">
-        <v>13.11928474903107</v>
+        <v>11.68397898674011</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>13.12621641159058</v>
+        <v>11.75161099433899</v>
       </c>
       <c r="C37" t="n">
-        <v>13.04380512237549</v>
+        <v>11.99645400047302</v>
       </c>
       <c r="D37" t="n">
-        <v>11.66629934310913</v>
+        <v>11.64738392829895</v>
       </c>
       <c r="E37" t="n">
-        <v>12.11248111724854</v>
+        <v>12.87029266357422</v>
       </c>
       <c r="F37" t="n">
-        <v>11.81632709503174</v>
+        <v>11.39738845825195</v>
       </c>
       <c r="G37" t="n">
-        <v>12.09909987449646</v>
+        <v>11.14452600479126</v>
       </c>
       <c r="H37" t="n">
-        <v>11.20638871192932</v>
+        <v>11.56398630142212</v>
       </c>
       <c r="I37" t="n">
-        <v>12.13498210906982</v>
+        <v>11.92449283599854</v>
       </c>
       <c r="J37" t="n">
-        <v>11.0687267780304</v>
+        <v>12.07361721992493</v>
       </c>
       <c r="K37" t="n">
-        <v>13.81013441085815</v>
+        <v>12.31550121307373</v>
       </c>
       <c r="L37" t="n">
-        <v>12.20844609737396</v>
+        <v>11.86852536201477</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>16.42634797096252</v>
+        <v>11.43427991867065</v>
       </c>
       <c r="C38" t="n">
-        <v>11.93052196502686</v>
+        <v>11.5650577545166</v>
       </c>
       <c r="D38" t="n">
-        <v>12.11102890968323</v>
+        <v>11.25084042549133</v>
       </c>
       <c r="E38" t="n">
-        <v>11.86617684364319</v>
+        <v>12.03179717063904</v>
       </c>
       <c r="F38" t="n">
-        <v>11.30219984054565</v>
+        <v>13.22267746925354</v>
       </c>
       <c r="G38" t="n">
-        <v>12.36737871170044</v>
+        <v>11.23779845237732</v>
       </c>
       <c r="H38" t="n">
-        <v>17.29654622077942</v>
+        <v>10.77148389816284</v>
       </c>
       <c r="I38" t="n">
-        <v>17.28904819488525</v>
+        <v>11.12658476829529</v>
       </c>
       <c r="J38" t="n">
-        <v>12.90710067749023</v>
+        <v>11.42235445976257</v>
       </c>
       <c r="K38" t="n">
-        <v>15.99251461029053</v>
+        <v>11.37843060493469</v>
       </c>
       <c r="L38" t="n">
-        <v>13.94888639450073</v>
+        <v>11.54413049221039</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>10.57900524139404</v>
+        <v>12.25556087493896</v>
       </c>
       <c r="C39" t="n">
-        <v>11.11561846733093</v>
+        <v>13.98238945007324</v>
       </c>
       <c r="D39" t="n">
-        <v>10.59995698928833</v>
+        <v>11.19697856903076</v>
       </c>
       <c r="E39" t="n">
-        <v>10.7930018901825</v>
+        <v>11.6568706035614</v>
       </c>
       <c r="F39" t="n">
-        <v>10.22048830986023</v>
+        <v>11.07485008239746</v>
       </c>
       <c r="G39" t="n">
-        <v>10.41493630409241</v>
+        <v>11.0000433921814</v>
       </c>
       <c r="H39" t="n">
-        <v>10.69873809814453</v>
+        <v>10.90443539619446</v>
       </c>
       <c r="I39" t="n">
-        <v>11.89775609970093</v>
+        <v>10.66190099716187</v>
       </c>
       <c r="J39" t="n">
-        <v>13.03787231445312</v>
+        <v>12.45232081413269</v>
       </c>
       <c r="K39" t="n">
-        <v>10.1277482509613</v>
+        <v>12.31123471260071</v>
       </c>
       <c r="L39" t="n">
-        <v>10.94851219654083</v>
+        <v>11.7496584892273</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>11.89472961425781</v>
+        <v>12.67424321174622</v>
       </c>
       <c r="C40" t="n">
-        <v>12.72907900810242</v>
+        <v>13.44175267219543</v>
       </c>
       <c r="D40" t="n">
-        <v>11.83288192749023</v>
+        <v>12.13060402870178</v>
       </c>
       <c r="E40" t="n">
-        <v>13.57724761962891</v>
+        <v>13.29119110107422</v>
       </c>
       <c r="F40" t="n">
-        <v>17.15533804893494</v>
+        <v>12.29118609428406</v>
       </c>
       <c r="G40" t="n">
-        <v>14.5073664188385</v>
+        <v>13.3617684841156</v>
       </c>
       <c r="H40" t="n">
-        <v>17.00471472740173</v>
+        <v>13.17083191871643</v>
       </c>
       <c r="I40" t="n">
-        <v>14.60234808921814</v>
+        <v>14.22505378723145</v>
       </c>
       <c r="J40" t="n">
-        <v>13.29889225959778</v>
+        <v>14.71832370758057</v>
       </c>
       <c r="K40" t="n">
-        <v>14.83358311653137</v>
+        <v>12.10250306129456</v>
       </c>
       <c r="L40" t="n">
-        <v>14.14361808300018</v>
+        <v>13.14074580669403</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>13.96068334579468</v>
+        <v>11.10065960884094</v>
       </c>
       <c r="C41" t="n">
-        <v>17.82963180541992</v>
+        <v>10.87724995613098</v>
       </c>
       <c r="D41" t="n">
-        <v>12.31978869438171</v>
+        <v>11.4153003692627</v>
       </c>
       <c r="E41" t="n">
-        <v>14.2120041847229</v>
+        <v>10.59197020530701</v>
       </c>
       <c r="F41" t="n">
-        <v>15.66002082824707</v>
+        <v>11.53968930244446</v>
       </c>
       <c r="G41" t="n">
-        <v>10.84668731689453</v>
+        <v>11.2048819065094</v>
       </c>
       <c r="H41" t="n">
-        <v>12.20630121231079</v>
+        <v>14.24194502830505</v>
       </c>
       <c r="I41" t="n">
-        <v>11.31893825531006</v>
+        <v>11.23479533195496</v>
       </c>
       <c r="J41" t="n">
-        <v>12.12519073486328</v>
+        <v>11.78238916397095</v>
       </c>
       <c r="K41" t="n">
-        <v>11.76923370361328</v>
+        <v>10.7196249961853</v>
       </c>
       <c r="L41" t="n">
-        <v>13.22484800815582</v>
+        <v>11.47085058689117</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>14.12771129608154</v>
+        <v>13.23563051223755</v>
       </c>
       <c r="C42" t="n">
-        <v>12.73521304130554</v>
+        <v>12.79376196861267</v>
       </c>
       <c r="D42" t="n">
-        <v>17.05171465873718</v>
+        <v>12.67504811286926</v>
       </c>
       <c r="E42" t="n">
-        <v>12.38057255744934</v>
+        <v>10.48724484443665</v>
       </c>
       <c r="F42" t="n">
-        <v>13.61804747581482</v>
+        <v>13.57224822044373</v>
       </c>
       <c r="G42" t="n">
-        <v>12.56928730010986</v>
+        <v>13.25005769729614</v>
       </c>
       <c r="H42" t="n">
-        <v>12.3923065662384</v>
+        <v>11.29066753387451</v>
       </c>
       <c r="I42" t="n">
-        <v>13.13060545921326</v>
+        <v>12.65115737915039</v>
       </c>
       <c r="J42" t="n">
-        <v>12.2920708656311</v>
+        <v>11.9186053276062</v>
       </c>
       <c r="K42" t="n">
-        <v>13.529940366745</v>
+        <v>14.42953181266785</v>
       </c>
       <c r="L42" t="n">
-        <v>13.38274695873261</v>
+        <v>12.6303953409195</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>14.79225897789001</v>
+        <v>13.8410656452179</v>
       </c>
       <c r="C43" t="n">
-        <v>13.40025639533997</v>
+        <v>11.681236743927</v>
       </c>
       <c r="D43" t="n">
-        <v>12.61109399795532</v>
+        <v>14.54472422599792</v>
       </c>
       <c r="E43" t="n">
-        <v>15.32492780685425</v>
+        <v>15.09477686882019</v>
       </c>
       <c r="F43" t="n">
-        <v>14.02538657188416</v>
+        <v>12.44124007225037</v>
       </c>
       <c r="G43" t="n">
-        <v>13.07798981666565</v>
+        <v>12.87950873374939</v>
       </c>
       <c r="H43" t="n">
-        <v>17.56594800949097</v>
+        <v>12.25117206573486</v>
       </c>
       <c r="I43" t="n">
-        <v>14.16001868247986</v>
+        <v>11.7843861579895</v>
       </c>
       <c r="J43" t="n">
-        <v>13.50108408927917</v>
+        <v>10.83983063697815</v>
       </c>
       <c r="K43" t="n">
-        <v>12.79106593132019</v>
+        <v>11.88563060760498</v>
       </c>
       <c r="L43" t="n">
-        <v>14.12500302791596</v>
+        <v>12.72435717582703</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>14.85982203483582</v>
+        <v>12.77034854888916</v>
       </c>
       <c r="C44" t="n">
-        <v>14.6529541015625</v>
+        <v>12.45977568626404</v>
       </c>
       <c r="D44" t="n">
-        <v>14.86739635467529</v>
+        <v>12.56483268737793</v>
       </c>
       <c r="E44" t="n">
-        <v>13.16996574401855</v>
+        <v>14.27952861785889</v>
       </c>
       <c r="F44" t="n">
-        <v>14.62306332588196</v>
+        <v>12.43737173080444</v>
       </c>
       <c r="G44" t="n">
-        <v>14.02494478225708</v>
+        <v>13.73353338241577</v>
       </c>
       <c r="H44" t="n">
-        <v>13.4959123134613</v>
+        <v>13.1211884021759</v>
       </c>
       <c r="I44" t="n">
-        <v>13.55423641204834</v>
+        <v>12.8104190826416</v>
       </c>
       <c r="J44" t="n">
-        <v>14.32834839820862</v>
+        <v>12.56353068351746</v>
       </c>
       <c r="K44" t="n">
-        <v>14.03703117370605</v>
+        <v>13.49918580055237</v>
       </c>
       <c r="L44" t="n">
-        <v>14.16136746406555</v>
+        <v>13.02397146224976</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>11.29876685142517</v>
+        <v>10.0075216293335</v>
       </c>
       <c r="C45" t="n">
-        <v>10.81840109825134</v>
+        <v>11.75859045982361</v>
       </c>
       <c r="D45" t="n">
-        <v>11.53675055503845</v>
+        <v>10.0926947593689</v>
       </c>
       <c r="E45" t="n">
-        <v>14.07986497879028</v>
+        <v>11.17898058891296</v>
       </c>
       <c r="F45" t="n">
-        <v>10.97744202613831</v>
+        <v>10.59897541999817</v>
       </c>
       <c r="G45" t="n">
-        <v>12.31953597068787</v>
+        <v>10.89418005943298</v>
       </c>
       <c r="H45" t="n">
-        <v>11.72931623458862</v>
+        <v>10.82449984550476</v>
       </c>
       <c r="I45" t="n">
-        <v>11.8631317615509</v>
+        <v>11.18700051307678</v>
       </c>
       <c r="J45" t="n">
-        <v>11.31054592132568</v>
+        <v>10.65930008888245</v>
       </c>
       <c r="K45" t="n">
-        <v>11.45251035690308</v>
+        <v>11.73642539978027</v>
       </c>
       <c r="L45" t="n">
-        <v>11.73862657546997</v>
+        <v>10.89381687641144</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>12.91749095916748</v>
+        <v>13.28775334358215</v>
       </c>
       <c r="C46" t="n">
-        <v>15.2356162071228</v>
+        <v>12.08228659629822</v>
       </c>
       <c r="D46" t="n">
-        <v>15.75677371025085</v>
+        <v>14.13361072540283</v>
       </c>
       <c r="E46" t="n">
-        <v>13.4038679599762</v>
+        <v>13.23734831809998</v>
       </c>
       <c r="F46" t="n">
-        <v>13.5034077167511</v>
+        <v>12.60890769958496</v>
       </c>
       <c r="G46" t="n">
-        <v>14.61210656166077</v>
+        <v>11.80296301841736</v>
       </c>
       <c r="H46" t="n">
-        <v>14.1810085773468</v>
+        <v>11.8428966999054</v>
       </c>
       <c r="I46" t="n">
-        <v>12.92342281341553</v>
+        <v>11.53615164756775</v>
       </c>
       <c r="J46" t="n">
-        <v>15.86605381965637</v>
+        <v>11.99453020095825</v>
       </c>
       <c r="K46" t="n">
-        <v>12.58792662620544</v>
+        <v>12.68376040458679</v>
       </c>
       <c r="L46" t="n">
-        <v>14.09876749515533</v>
+        <v>12.52102086544037</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>12.67889761924744</v>
+        <v>11.38059306144714</v>
       </c>
       <c r="C47" t="n">
-        <v>11.65811800956726</v>
+        <v>15.74715733528137</v>
       </c>
       <c r="D47" t="n">
-        <v>13.24160575866699</v>
+        <v>14.67822694778442</v>
       </c>
       <c r="E47" t="n">
-        <v>12.44841933250427</v>
+        <v>12.88522243499756</v>
       </c>
       <c r="F47" t="n">
-        <v>18.38247346878052</v>
+        <v>11.03001546859741</v>
       </c>
       <c r="G47" t="n">
-        <v>14.74153780937195</v>
+        <v>12.38456153869629</v>
       </c>
       <c r="H47" t="n">
-        <v>13.1876072883606</v>
+        <v>12.88322377204895</v>
       </c>
       <c r="I47" t="n">
-        <v>14.08842301368713</v>
+        <v>12.16705012321472</v>
       </c>
       <c r="J47" t="n">
-        <v>13.28659868240356</v>
+        <v>12.62387681007385</v>
       </c>
       <c r="K47" t="n">
-        <v>12.68547129631042</v>
+        <v>11.550133228302</v>
       </c>
       <c r="L47" t="n">
-        <v>13.63991522789001</v>
+        <v>12.73300607204437</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>13.29796195030212</v>
+        <v>13.7502384185791</v>
       </c>
       <c r="C48" t="n">
-        <v>14.70209956169128</v>
+        <v>14.41852259635925</v>
       </c>
       <c r="D48" t="n">
-        <v>13.20934319496155</v>
+        <v>12.61735701560974</v>
       </c>
       <c r="E48" t="n">
-        <v>13.92164969444275</v>
+        <v>11.93813920021057</v>
       </c>
       <c r="F48" t="n">
-        <v>13.56691288948059</v>
+        <v>13.38793349266052</v>
       </c>
       <c r="G48" t="n">
-        <v>14.33486366271973</v>
+        <v>12.54962849617004</v>
       </c>
       <c r="H48" t="n">
-        <v>14.42914009094238</v>
+        <v>11.49723267555237</v>
       </c>
       <c r="I48" t="n">
-        <v>13.16455030441284</v>
+        <v>11.56609344482422</v>
       </c>
       <c r="J48" t="n">
-        <v>13.90670228004456</v>
+        <v>11.56107449531555</v>
       </c>
       <c r="K48" t="n">
-        <v>15.55974793434143</v>
+        <v>12.75953888893127</v>
       </c>
       <c r="L48" t="n">
-        <v>14.00929715633392</v>
+        <v>12.60457587242126</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>13.26566576957703</v>
+        <v>12.11770296096802</v>
       </c>
       <c r="C49" t="n">
-        <v>13.11922860145569</v>
+        <v>11.8299446105957</v>
       </c>
       <c r="D49" t="n">
-        <v>18.02403330802917</v>
+        <v>11.3486442565918</v>
       </c>
       <c r="E49" t="n">
-        <v>12.30567908287048</v>
+        <v>11.73070168495178</v>
       </c>
       <c r="F49" t="n">
-        <v>12.5455162525177</v>
+        <v>12.9256808757782</v>
       </c>
       <c r="G49" t="n">
-        <v>12.97981286048889</v>
+        <v>12.15160131454468</v>
       </c>
       <c r="H49" t="n">
-        <v>12.7757351398468</v>
+        <v>11.72963619232178</v>
       </c>
       <c r="I49" t="n">
-        <v>12.35407757759094</v>
+        <v>11.09328627586365</v>
       </c>
       <c r="J49" t="n">
-        <v>12.76378178596497</v>
+        <v>14.05722069740295</v>
       </c>
       <c r="K49" t="n">
-        <v>12.00630855560303</v>
+        <v>11.56807708740234</v>
       </c>
       <c r="L49" t="n">
-        <v>13.21398389339447</v>
+        <v>12.05524959564209</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>12.03317928314209</v>
+        <v>12.02443265914917</v>
       </c>
       <c r="C50" t="n">
-        <v>14.46399545669556</v>
+        <v>11.33864736557007</v>
       </c>
       <c r="D50" t="n">
-        <v>12.46495985984802</v>
+        <v>11.47383427619934</v>
       </c>
       <c r="E50" t="n">
-        <v>12.79513382911682</v>
+        <v>10.89478302001953</v>
       </c>
       <c r="F50" t="n">
-        <v>13.21456122398376</v>
+        <v>11.37406229972839</v>
       </c>
       <c r="G50" t="n">
-        <v>12.326575756073</v>
+        <v>11.60403156280518</v>
       </c>
       <c r="H50" t="n">
-        <v>12.98538875579834</v>
+        <v>11.30876874923706</v>
       </c>
       <c r="I50" t="n">
-        <v>13.7162504196167</v>
+        <v>10.88790774345398</v>
       </c>
       <c r="J50" t="n">
-        <v>12.49994707107544</v>
+        <v>11.54913020133972</v>
       </c>
       <c r="K50" t="n">
-        <v>13.95465397834778</v>
+        <v>11.73282742500305</v>
       </c>
       <c r="L50" t="n">
-        <v>13.04546456336975</v>
+        <v>11.41884253025055</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>11.70460486412048</v>
+        <v>10.29576301574707</v>
       </c>
       <c r="C51" t="n">
-        <v>11.36560440063477</v>
+        <v>10.20450329780579</v>
       </c>
       <c r="D51" t="n">
-        <v>12.05829858779907</v>
+        <v>10.64633965492249</v>
       </c>
       <c r="E51" t="n">
-        <v>11.64832186698914</v>
+        <v>10.44285368919373</v>
       </c>
       <c r="F51" t="n">
-        <v>11.87103986740112</v>
+        <v>10.6661171913147</v>
       </c>
       <c r="G51" t="n">
-        <v>11.8431293964386</v>
+        <v>10.7092616558075</v>
       </c>
       <c r="H51" t="n">
-        <v>12.02760982513428</v>
+        <v>10.1503005027771</v>
       </c>
       <c r="I51" t="n">
-        <v>11.9133517742157</v>
+        <v>10.79757857322693</v>
       </c>
       <c r="J51" t="n">
-        <v>11.5806086063385</v>
+        <v>10.75708556175232</v>
       </c>
       <c r="K51" t="n">
-        <v>12.12399005889893</v>
+        <v>10.88810110092163</v>
       </c>
       <c r="L51" t="n">
-        <v>11.81365592479706</v>
+        <v>10.55579042434692</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.33778080463409</v>
+        <v>12.08858813285828</v>
       </c>
       <c r="C52" t="n">
-        <v>12.42044386863708</v>
+        <v>12.24635159015656</v>
       </c>
       <c r="D52" t="n">
-        <v>12.62164872646332</v>
+        <v>12.02576374530792</v>
       </c>
       <c r="E52" t="n">
-        <v>12.43406650066376</v>
+        <v>12.17673170089722</v>
       </c>
       <c r="F52" t="n">
-        <v>12.56332628726959</v>
+        <v>12.0295515537262</v>
       </c>
       <c r="G52" t="n">
-        <v>12.33865362644196</v>
+        <v>12.17478863239288</v>
       </c>
       <c r="H52" t="n">
-        <v>12.67644909381866</v>
+        <v>12.12763602256775</v>
       </c>
       <c r="I52" t="n">
-        <v>12.46825579166412</v>
+        <v>11.77513906955719</v>
       </c>
       <c r="J52" t="n">
-        <v>12.43482063770294</v>
+        <v>12.33645406723022</v>
       </c>
       <c r="K52" t="n">
-        <v>12.81892365455627</v>
+        <v>12.26396819114685</v>
       </c>
       <c r="L52" t="n">
-        <v>12.51143689918518</v>
+        <v>12.12449727058411</v>
       </c>
     </row>
   </sheetData>
